--- a/docs/examples/Sentinel-Wildlife/Sentinel-Wildlife_results.xlsx
+++ b/docs/examples/Sentinel-Wildlife/Sentinel-Wildlife_results.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methods &amp; Rules" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ranked Results'!$A$1:$Y$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ranked Results'!$A$1:$Z$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Species Ranking'!$A$1:$T$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Observation Inventory'!$A$1:$G$401</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Observations by County'!$A$1:$G$197</definedName>
@@ -36,9 +36,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Host-Pathogen Links'!$A$1:$E$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'NDE Taxon Overlap'!$A$1:$E$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Human Evidence'!$A$1:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Place Context'!$A$1:$J$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Place Context'!$A$1:$K$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'County Bridge'!$A$1:$C$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Methods &amp; Rules'!$A$1:$B$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Methods &amp; Rules'!$A$1:$B$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y65"/>
+  <dimension ref="A1:Z65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -514,11 +514,12 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="46" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="46" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -589,60 +590,65 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>EPA FRS facilities</t>
+          <t>EPA PFAS facilities</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>EPA FRS facilities (all)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>spoke-okn chemicals in county</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>adult asthma %</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>per-capita income USD</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>climatemodelskg places</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>climate papers</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>contaminant samples in county</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>county bridge</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>anchor lat</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>anchor lon</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>supporting KGs</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
@@ -668,7 +674,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9622652344795564</v>
+        <v>0.957738898518082</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>11</v>
@@ -697,43 +703,46 @@
         <v>24</v>
       </c>
       <c r="N2" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>8727</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="P2" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>31409</v>
       </c>
-      <c r="R2" s="2" t="n">
+      <c r="S2" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="S2" s="2" t="n">
+      <c r="T2" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="T2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="W2" s="2" t="n">
         <v>28.49932056076961</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="X2" s="2" t="n">
         <v>-81.57973854557652</v>
       </c>
-      <c r="X2" s="2" t="n">
+      <c r="Y2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>11 sentinel-capable sp. (best tier M); 4 pathogen-host sp.; 110 spp. observed (86 bird / 24 amphibian); 8,727 EPA FRS facilities; adult asthma 8.3%; contaminant samples in county: 0</t>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>11 sentinel-capable sp. (best tier M); 4 pathogen-host sp.; 110 spp. observed (86 bird / 24 amphibian); 210 EPA PFAS facilities of 8,727 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -757,7 +766,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.718961203301602</v>
+        <v>0.7177835666404461</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>4</v>
@@ -786,43 +795,46 @@
         <v>19</v>
       </c>
       <c r="N3" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="O3" s="2" t="n">
         <v>9284</v>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="P3" s="2" t="n">
         <v>146</v>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="Q3" s="2" t="n">
         <v>7.7</v>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>29598</v>
       </c>
-      <c r="R3" s="2" t="n">
+      <c r="S3" s="2" t="n">
         <v>51</v>
       </c>
-      <c r="S3" s="2" t="n">
+      <c r="T3" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="T3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V3" s="2" t="n">
+      <c r="W3" s="2" t="n">
         <v>25.58527936881842</v>
       </c>
-      <c r="W3" s="2" t="n">
+      <c r="X3" s="2" t="n">
         <v>-80.70451265047141</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="Y3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>4 sentinel-capable sp. (best tier I1); 4 pathogen-host sp.; 107 spp. observed (88 bird / 19 amphibian); 9,284 EPA FRS facilities; adult asthma 7.7%; contaminant samples in county: 0</t>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>4 sentinel-capable sp. (best tier I1); 4 pathogen-host sp.; 107 spp. observed (88 bird / 19 amphibian); 264 EPA PFAS facilities of 9,284 FRS records; adult asthma 7.7%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -846,7 +858,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.6724047738484171</v>
+        <v>0.6706998885421401</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>5</v>
@@ -875,43 +887,46 @@
         <v>19</v>
       </c>
       <c r="N4" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="O4" s="2" t="n">
         <v>6717</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="P4" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="Q4" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="R4" s="2" t="n">
         <v>40957</v>
       </c>
-      <c r="R4" s="2" t="n">
+      <c r="S4" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="S4" s="2" t="n">
+      <c r="T4" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="T4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="W4" s="2" t="n">
         <v>26.69963254942522</v>
       </c>
-      <c r="W4" s="2" t="n">
+      <c r="X4" s="2" t="n">
         <v>-79.99199953131671</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="Y4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>5 sentinel-capable sp. (best tier I2); 4 pathogen-host sp.; 81 spp. observed (62 bird / 19 amphibian); 6,717 EPA FRS facilities; adult asthma 8.0%; contaminant samples in county: 0</t>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>5 sentinel-capable sp. (best tier I2); 4 pathogen-host sp.; 81 spp. observed (62 bird / 19 amphibian); 177 EPA PFAS facilities of 6,717 FRS records; adult asthma 8.0%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -935,7 +950,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.5351853058531855</v>
+        <v>0.54648085182886</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>6</v>
@@ -964,43 +979,46 @@
         <v>13</v>
       </c>
       <c r="N5" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="O5" s="2" t="n">
         <v>3929</v>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="P5" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="Q5" s="2" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="R5" s="2" t="n">
         <v>33662</v>
       </c>
-      <c r="R5" s="2" t="n">
+      <c r="S5" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="S5" s="2" t="n">
+      <c r="T5" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="T5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V5" s="2" t="n">
+      <c r="W5" s="2" t="n">
         <v>28.24594282536288</v>
       </c>
-      <c r="W5" s="2" t="n">
+      <c r="X5" s="2" t="n">
         <v>-80.83038906677767</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="Y5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>6 sentinel-capable sp. (best tier I1); 0 pathogen-host sp.; 84 spp. observed (71 bird / 13 amphibian); 3,929 EPA FRS facilities; adult asthma 8.3%; contaminant samples in county: 0</t>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>6 sentinel-capable sp. (best tier I1); 0 pathogen-host sp.; 84 spp. observed (71 bird / 13 amphibian); 175 EPA PFAS facilities of 3,929 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1042,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.515898944618056</v>
+        <v>0.5301112841865725</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>5</v>
@@ -1053,43 +1071,46 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="O6" s="2" t="n">
         <v>1505</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="P6" s="2" t="n">
+      <c r="Q6" s="2" t="n">
         <v>9.1</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="R6" s="2" t="n">
         <v>29821</v>
       </c>
-      <c r="R6" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="S6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="T6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="W6" s="2" t="n">
         <v>29.74767936437791</v>
       </c>
-      <c r="W6" s="2" t="n">
+      <c r="X6" s="2" t="n">
         <v>-82.4299425913659</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="Y6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>5 sentinel-capable sp. (best tier I1); 0 pathogen-host sp.; 99 spp. observed (73 bird / 26 amphibian); 1,505 EPA FRS facilities; adult asthma 9.1%; contaminant samples in county: 0</t>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>5 sentinel-capable sp. (best tier I1); 0 pathogen-host sp.; 99 spp. observed (73 bird / 26 amphibian); 66 EPA PFAS facilities of 1,505 FRS records; adult asthma 9.1%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1134,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.5087604194256675</v>
+        <v>0.5177059279286117</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>2</v>
@@ -1142,43 +1163,46 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="O7" s="2" t="n">
         <v>5182</v>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="P7" s="2" t="n">
+      <c r="Q7" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="R7" s="2" t="n">
         <v>25820</v>
       </c>
-      <c r="R7" s="2" t="n">
+      <c r="S7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="S7" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="T7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V7" s="2" t="n">
+      <c r="W7" s="2" t="n">
         <v>27.67591672557383</v>
       </c>
-      <c r="W7" s="2" t="n">
+      <c r="X7" s="2" t="n">
         <v>-81.48039780891368</v>
       </c>
-      <c r="X7" s="2" t="n">
+      <c r="Y7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>2 sentinel-capable sp. (best tier M); 1 pathogen-host sp.; 62 spp. observed (36 bird / 26 amphibian); 5,182 EPA FRS facilities; adult asthma 9.0%; contaminant samples in county: 0</t>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>2 sentinel-capable sp. (best tier M); 1 pathogen-host sp.; 62 spp. observed (36 bird / 26 amphibian); 216 EPA PFAS facilities of 5,182 FRS records; adult asthma 9.0%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1226,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.4849018977902184</v>
+        <v>0.490742369595457</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>5</v>
@@ -1231,43 +1255,46 @@
         <v>32</v>
       </c>
       <c r="N8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="P8" s="2" t="n">
+      <c r="Q8" s="2" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="R8" s="2" t="n">
         <v>28320</v>
       </c>
-      <c r="R8" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V8" s="2" t="n">
+      <c r="W8" s="2" t="n">
         <v>30.12320046555866</v>
       </c>
-      <c r="W8" s="2" t="n">
+      <c r="X8" s="2" t="n">
         <v>-84.60080170880354</v>
       </c>
-      <c r="X8" s="2" t="n">
+      <c r="Y8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>5 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 73 spp. observed (41 bird / 32 amphibian); 188 EPA FRS facilities; adult asthma 8.6%; contaminant samples in county: 0</t>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>5 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 73 spp. observed (41 bird / 32 amphibian); 4 EPA PFAS facilities of 188 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1318,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.4478046435131751</v>
+        <v>0.4503698484369158</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
@@ -1320,43 +1347,46 @@
         <v>24</v>
       </c>
       <c r="N9" s="2" t="n">
+        <v>279</v>
+      </c>
+      <c r="O9" s="2" t="n">
         <v>8368</v>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>144</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="Q9" s="2" t="n">
         <v>8.1</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>33616</v>
       </c>
-      <c r="R9" s="2" t="n">
+      <c r="S9" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="S9" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V9" s="2" t="n">
+      <c r="W9" s="2" t="n">
         <v>28.01014547715257</v>
       </c>
-      <c r="W9" s="2" t="n">
+      <c r="X9" s="2" t="n">
         <v>-82.418986425114</v>
       </c>
-      <c r="X9" s="2" t="n">
+      <c r="Y9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 62 spp. observed (38 bird / 24 amphibian); 8,368 EPA FRS facilities; adult asthma 8.1%; contaminant samples in county: 0</t>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 62 spp. observed (38 bird / 24 amphibian); 279 EPA PFAS facilities of 8,368 FRS records; adult asthma 8.1%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1396,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Leon</t>
+          <t>Pinellas</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1380,72 +1410,75 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.4341040206580183</v>
+        <v>0.4490567988277519</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1792</v>
+        <v>270</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>141</v>
+        <v>4891</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>9.1</v>
+        <v>149</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>31778</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>1</v>
+        <v>36754</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V10" s="2" t="n">
-        <v>30.45472026465805</v>
-      </c>
       <c r="W10" s="2" t="n">
-        <v>-84.28561742869873</v>
+        <v>27.86565155117322</v>
       </c>
       <c r="X10" s="2" t="n">
+        <v>-82.98420050849229</v>
+      </c>
+      <c r="Y10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>3 sentinel-capable sp. (best tier M); 0 pathogen-host sp.; 39 spp. observed (16 bird / 23 amphibian); 1,792 EPA FRS facilities; adult asthma 9.1%; contaminant samples in county: 0</t>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>3 sentinel-capable sp. (best tier I2); 1 pathogen-host sp.; 49 spp. observed (40 bird / 9 amphibian); 270 EPA PFAS facilities of 4,891 FRS records; adult asthma 8.7%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1488,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Pinellas</t>
+          <t>Sarasota</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>12115</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1469,7 +1502,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.4339289443949667</v>
+        <v>0.4333548694002401</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>3</v>
@@ -1483,58 +1516,61 @@
         <v>1</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>4891</v>
+        <v>104</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>149</v>
+        <v>2489</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>145</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>36754</v>
+        <v>8</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>12</v>
+        <v>44402</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V11" s="2" t="n">
-        <v>27.86565155117322</v>
-      </c>
       <c r="W11" s="2" t="n">
-        <v>-82.98420050849229</v>
+        <v>27.32019707772083</v>
       </c>
       <c r="X11" s="2" t="n">
+        <v>-82.60251750242672</v>
+      </c>
+      <c r="Y11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>3 sentinel-capable sp. (best tier I2); 1 pathogen-host sp.; 49 spp. observed (40 bird / 9 amphibian); 4,891 EPA FRS facilities; adult asthma 8.7%; contaminant samples in county: 0</t>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>3 sentinel-capable sp. (best tier I2); 1 pathogen-host sp.; 63 spp. observed (53 bird / 10 amphibian); 104 EPA PFAS facilities of 2,489 FRS records; adult asthma 8.0%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1580,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Sarasota</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12115</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1558,72 +1594,75 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.4218757027100831</v>
+        <v>0.427903072096473</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>I2</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>2489</v>
+        <v>31</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>145</v>
+        <v>1792</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>44402</v>
+        <v>9.1</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>3</v>
+        <v>31778</v>
       </c>
       <c r="S12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>30.45472026465805</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>-84.28561742869873</v>
+      </c>
+      <c r="Y12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="T12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="n">
-        <v>27.32019707772083</v>
-      </c>
-      <c r="W12" s="2" t="n">
-        <v>-82.60251750242672</v>
-      </c>
-      <c r="X12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>3 sentinel-capable sp. (best tier I2); 1 pathogen-host sp.; 63 spp. observed (53 bird / 10 amphibian); 2,489 EPA FRS facilities; adult asthma 8.0%; contaminant samples in county: 0</t>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>3 sentinel-capable sp. (best tier M); 0 pathogen-host sp.; 39 spp. observed (16 bird / 23 amphibian); 31 EPA PFAS facilities of 1,792 FRS records; adult asthma 9.1%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1672,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Pasco</t>
+          <t>Manatee</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1647,7 +1686,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.4158148754346232</v>
+        <v>0.4235955111586185</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>2</v>
@@ -1661,58 +1700,61 @@
         <v>2</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2752</v>
+        <v>79</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>143</v>
+        <v>2059</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>8.4</v>
+        <v>146</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>29498</v>
+        <v>8.6</v>
       </c>
       <c r="R13" s="2" t="n">
+        <v>35146</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>27.52895944163995</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>-82.42958379039023</v>
+      </c>
+      <c r="Y13" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="S13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="n">
-        <v>28.27818395167066</v>
-      </c>
-      <c r="W13" s="2" t="n">
-        <v>-82.7176991548576</v>
-      </c>
-      <c r="X13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>2 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 31 spp. observed (15 bird / 16 amphibian); 2,752 EPA FRS facilities; adult asthma 8.4%; contaminant samples in county: 0</t>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 32 spp. observed (24 bird / 8 amphibian); 79 EPA PFAS facilities of 2,059 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1764,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Manatee</t>
+          <t>Collier</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1736,72 +1778,75 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.4132917523922464</v>
+        <v>0.4187911356346398</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>I2</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>2059</v>
+        <v>69</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>146</v>
+        <v>1900</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>8.6</v>
+        <v>143</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>35146</v>
+        <v>7.6</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>3</v>
+        <v>46785</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V14" s="2" t="n">
-        <v>27.52895944163995</v>
-      </c>
       <c r="W14" s="2" t="n">
-        <v>-82.42958379039023</v>
+        <v>26.12475077294162</v>
       </c>
       <c r="X14" s="2" t="n">
+        <v>-81.14631612119349</v>
+      </c>
+      <c r="Y14" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>2 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 32 spp. observed (24 bird / 8 amphibian); 2,059 EPA FRS facilities; adult asthma 8.6%; contaminant samples in county: 0</t>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2 sentinel-capable sp. (best tier I4); 3 pathogen-host sp.; 70 spp. observed (52 bird / 18 amphibian); 69 EPA PFAS facilities of 1,900 FRS records; adult asthma 7.6%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1856,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Pasco</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1825,72 +1870,75 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.4111010100157545</v>
+        <v>0.4163770987404868</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>5093</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>145</v>
+        <v>2752</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>143</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>34818</v>
+        <v>8.4</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>8</v>
+        <v>29498</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U15" s="2" t="inlineStr">
+      <c r="U15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V15" s="2" t="n">
-        <v>26.7466051081053</v>
-      </c>
       <c r="W15" s="2" t="n">
-        <v>-81.95127561002303</v>
+        <v>28.27818395167066</v>
       </c>
       <c r="X15" s="2" t="n">
+        <v>-82.7176991548576</v>
+      </c>
+      <c r="Y15" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I1); 1 pathogen-host sp.; 47 spp. observed (34 bird / 13 amphibian); 5,093 EPA FRS facilities; adult asthma 8.3%; contaminant samples in county: 0</t>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 31 spp. observed (15 bird / 16 amphibian); 70 EPA PFAS facilities of 2,752 FRS records; adult asthma 8.4%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -1900,12 +1948,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Collier</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1914,72 +1962,75 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.4093868624329601</v>
+        <v>0.4075905539395993</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1900</v>
+        <v>118</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>143</v>
+        <v>5093</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>7.6</v>
+        <v>145</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>46785</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>5</v>
+        <v>34818</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="U16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V16" s="2" t="n">
-        <v>26.12475077294162</v>
-      </c>
       <c r="W16" s="2" t="n">
-        <v>-81.14631612119349</v>
+        <v>26.7466051081053</v>
       </c>
       <c r="X16" s="2" t="n">
+        <v>-81.95127561002303</v>
+      </c>
+      <c r="Y16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>2 sentinel-capable sp. (best tier I4); 3 pathogen-host sp.; 70 spp. observed (52 bird / 18 amphibian); 1,900 EPA FRS facilities; adult asthma 7.6%; contaminant samples in county: 0</t>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I1); 1 pathogen-host sp.; 47 spp. observed (34 bird / 13 amphibian); 118 EPA PFAS facilities of 5,093 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2054,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.3974696281685738</v>
+        <v>0.400254787918441</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
@@ -2032,43 +2083,46 @@
         <v>18</v>
       </c>
       <c r="N17" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="O17" s="2" t="n">
         <v>1070</v>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="P17" s="2" t="n">
         <v>143</v>
       </c>
-      <c r="P17" s="2" t="n">
+      <c r="Q17" s="2" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q17" s="2" t="n">
+      <c r="R17" s="2" t="n">
         <v>26520</v>
       </c>
-      <c r="R17" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="S17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="U17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V17" s="2" t="n">
+      <c r="W17" s="2" t="n">
         <v>28.58129013344362</v>
       </c>
-      <c r="W17" s="2" t="n">
+      <c r="X17" s="2" t="n">
         <v>-82.65724067139712</v>
       </c>
-      <c r="X17" s="2" t="n">
+      <c r="Y17" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier M); 1 pathogen-host sp.; 30 spp. observed (12 bird / 18 amphibian); 1,070 EPA FRS facilities; adult asthma 8.6%; contaminant samples in county: 0</t>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier M); 1 pathogen-host sp.; 30 spp. observed (12 bird / 18 amphibian); 26 EPA PFAS facilities of 1,070 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2146,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3570872847520412</v>
+        <v>0.3637476777104381</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>2</v>
@@ -2121,43 +2175,46 @@
         <v>7</v>
       </c>
       <c r="N18" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="O18" s="4" t="n">
         <v>975</v>
       </c>
-      <c r="O18" s="4" t="n">
+      <c r="P18" s="4" t="n">
         <v>142</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="Q18" s="4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q18" s="4" t="n">
+      <c r="R18" s="4" t="n">
         <v>33275</v>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="S18" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="S18" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U18" s="4" t="inlineStr">
+      <c r="U18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V18" s="4" t="n">
+      <c r="W18" s="4" t="n">
         <v>26.95249181095944</v>
       </c>
-      <c r="W18" s="4" t="n">
+      <c r="X18" s="4" t="n">
         <v>-82.00575596076499</v>
       </c>
-      <c r="X18" s="4" t="n">
+      <c r="Y18" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Y18" s="5" t="inlineStr">
-        <is>
-          <t>2 sentinel-capable sp. (best tier I3); 2 pathogen-host sp.; 31 spp. observed (24 bird / 7 amphibian); 975 EPA FRS facilities; adult asthma 8.8%; contaminant samples in county: 0</t>
+      <c r="Z18" s="4" t="inlineStr">
+        <is>
+          <t>2 sentinel-capable sp. (best tier I3); 2 pathogen-host sp.; 31 spp. observed (24 bird / 7 amphibian); 28 EPA PFAS facilities of 975 FRS records; adult asthma 8.8%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2238,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3422013543135219</v>
+        <v>0.3511856727700408</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>1</v>
@@ -2210,43 +2267,46 @@
         <v>16</v>
       </c>
       <c r="N19" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="O19" s="4" t="n">
         <v>1155</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="P19" s="4" t="n">
         <v>141</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="Q19" s="4" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q19" s="4" t="n">
+      <c r="R19" s="4" t="n">
         <v>32037</v>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="S19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="S19" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U19" s="4" t="inlineStr">
+      <c r="U19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V19" s="4" t="n">
+      <c r="W19" s="4" t="n">
         <v>30.06037823345315</v>
       </c>
-      <c r="W19" s="4" t="n">
+      <c r="X19" s="4" t="n">
         <v>-81.82769081121819</v>
       </c>
-      <c r="X19" s="4" t="n">
+      <c r="Y19" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Y19" s="5" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier M); 0 pathogen-host sp.; 24 spp. observed (8 bird / 16 amphibian); 1,155 EPA FRS facilities; adult asthma 8.6%; contaminant samples in county: 0</t>
+      <c r="Z19" s="4" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier M); 0 pathogen-host sp.; 24 spp. observed (8 bird / 16 amphibian); 38 EPA PFAS facilities of 1,155 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2330,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3295783416921635</v>
+        <v>0.347458241110973</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>3</v>
@@ -2299,43 +2359,46 @@
         <v>13</v>
       </c>
       <c r="N20" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="O20" s="4" t="n">
         <v>619</v>
       </c>
-      <c r="O20" s="4" t="n">
+      <c r="P20" s="4" t="n">
         <v>142</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="Q20" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q20" s="4" t="n">
+      <c r="R20" s="4" t="n">
         <v>28174</v>
       </c>
-      <c r="R20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U20" s="4" t="inlineStr">
+      <c r="U20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V20" s="4" t="n">
+      <c r="W20" s="4" t="n">
         <v>28.82893634608188</v>
       </c>
-      <c r="W20" s="4" t="n">
+      <c r="X20" s="4" t="n">
         <v>-82.66738038119389</v>
       </c>
-      <c r="X20" s="4" t="n">
+      <c r="Y20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Y20" s="5" t="inlineStr">
-        <is>
-          <t>3 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 39 spp. observed (26 bird / 13 amphibian); 619 EPA FRS facilities; adult asthma 9.2%; contaminant samples in county: 0</t>
+      <c r="Z20" s="4" t="inlineStr">
+        <is>
+          <t>3 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 39 spp. observed (26 bird / 13 amphibian); 28 EPA PFAS facilities of 619 FRS records; adult asthma 9.2%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2422,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.3258814908950289</v>
+        <v>0.3463198345825966</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>2</v>
@@ -2388,43 +2451,46 @@
         <v>19</v>
       </c>
       <c r="N21" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="O21" s="4" t="n">
         <v>1015</v>
       </c>
-      <c r="O21" s="4" t="n">
+      <c r="P21" s="4" t="n">
         <v>144</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="Q21" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q21" s="4" t="n">
+      <c r="R21" s="4" t="n">
         <v>32322</v>
       </c>
-      <c r="R21" s="4" t="n">
+      <c r="S21" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="S21" s="4" t="n">
+      <c r="T21" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
+      <c r="U21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V21" s="4" t="n">
+      <c r="W21" s="4" t="n">
         <v>30.9845463980149</v>
       </c>
-      <c r="W21" s="4" t="n">
+      <c r="X21" s="4" t="n">
         <v>-86.96393265524841</v>
       </c>
-      <c r="X21" s="4" t="n">
+      <c r="Y21" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Y21" s="5" t="inlineStr">
-        <is>
-          <t>2 sentinel-capable sp. (best tier I1); 0 pathogen-host sp.; 28 spp. observed (9 bird / 19 amphibian); 1,015 EPA FRS facilities; adult asthma 8.3%; contaminant samples in county: 0</t>
+      <c r="Z21" s="4" t="inlineStr">
+        <is>
+          <t>2 sentinel-capable sp. (best tier I1); 0 pathogen-host sp.; 28 spp. observed (9 bird / 19 amphibian); 56 EPA PFAS facilities of 1,015 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2500,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Marion</t>
+          <t>Highlands</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -2448,48 +2514,48 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.3112066221578808</v>
+        <v>0.3185532168812246</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>I2</t>
+          <t>I3</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2419</v>
+        <v>39</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>144</v>
+        <v>753</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>9</v>
+        <v>141</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>26990</v>
+        <v>8.6</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1</v>
+        <v>27979</v>
       </c>
       <c r="S22" s="4" t="n">
         <v>0</v>
@@ -2497,23 +2563,26 @@
       <c r="T22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U22" s="4" t="inlineStr">
+      <c r="U22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V22" s="4" t="n">
-        <v>29.36382786445562</v>
-      </c>
       <c r="W22" s="4" t="n">
-        <v>-82.16948793283655</v>
+        <v>27.33940919936872</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y22" s="5" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 44 spp. observed (20 bird / 24 amphibian); 2,419 EPA FRS facilities; adult asthma 9.0%; contaminant samples in county: 0</t>
+        <v>-81.3746008289168</v>
+      </c>
+      <c r="Y22" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="4" t="inlineStr">
+        <is>
+          <t>2 sentinel-capable sp. (best tier I3); 1 pathogen-host sp.; 32 spp. observed (14 bird / 18 amphibian); 39 EPA PFAS facilities of 753 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2592,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Broward</t>
+          <t>Marion</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2537,7 +2606,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.298716734859156</v>
+        <v>0.3164240105416022</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>1</v>
@@ -2551,58 +2620,61 @@
         <v>0</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>7302</v>
+        <v>75</v>
       </c>
       <c r="O23" s="4" t="n">
+        <v>2419</v>
+      </c>
+      <c r="P23" s="4" t="n">
         <v>144</v>
       </c>
-      <c r="P23" s="4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="Q23" s="4" t="n">
-        <v>34063</v>
+        <v>9</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>24</v>
+        <v>26990</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U23" s="4" t="inlineStr">
+      <c r="U23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V23" s="4" t="n">
-        <v>26.11823749256257</v>
-      </c>
       <c r="W23" s="4" t="n">
-        <v>-80.55238011597748</v>
+        <v>29.36382786445562</v>
       </c>
       <c r="X23" s="4" t="n">
+        <v>-82.16948793283655</v>
+      </c>
+      <c r="Y23" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Y23" s="5" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 28 spp. observed (20 bird / 8 amphibian); 7,302 EPA FRS facilities; adult asthma 7.8%; contaminant samples in county: 0</t>
+      <c r="Z23" s="4" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 44 spp. observed (20 bird / 24 amphibian); 75 EPA PFAS facilities of 2,419 FRS records; adult asthma 9.0%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2612,12 +2684,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Highlands</t>
+          <t>Broward</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2626,72 +2698,75 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2984512960869402</v>
+        <v>0.3037101305359748</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>I3</t>
+          <t>I2</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>753</v>
+        <v>267</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>141</v>
+        <v>7302</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>8.6</v>
+        <v>144</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>27979</v>
+        <v>7.8</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0</v>
+        <v>34063</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U24" s="4" t="inlineStr">
+      <c r="U24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V24" s="4" t="n">
-        <v>27.33940919936872</v>
-      </c>
       <c r="W24" s="4" t="n">
-        <v>-81.3746008289168</v>
+        <v>26.11823749256257</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="5" t="inlineStr">
-        <is>
-          <t>2 sentinel-capable sp. (best tier I3); 1 pathogen-host sp.; 32 spp. observed (14 bird / 18 amphibian); 753 EPA FRS facilities; adult asthma 8.6%; contaminant samples in county: 0</t>
+        <v>-80.55238011597748</v>
+      </c>
+      <c r="Y24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z24" s="4" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 28 spp. observed (20 bird / 8 amphibian); 267 EPA PFAS facilities of 7,302 FRS records; adult asthma 7.8%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2790,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.2915142434797146</v>
+        <v>0.2964049264419756</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>1</v>
@@ -2744,43 +2819,46 @@
         <v>13</v>
       </c>
       <c r="N25" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="O25" s="4" t="n">
         <v>1787</v>
       </c>
-      <c r="O25" s="4" t="n">
+      <c r="P25" s="4" t="n">
         <v>142</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="Q25" s="4" t="n">
         <v>8.1</v>
       </c>
-      <c r="Q25" s="4" t="n">
+      <c r="R25" s="4" t="n">
         <v>24146</v>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="S25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="S25" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U25" s="4" t="inlineStr">
+      <c r="U25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V25" s="4" t="n">
+      <c r="W25" s="4" t="n">
         <v>28.25779299285393</v>
       </c>
-      <c r="W25" s="4" t="n">
+      <c r="X25" s="4" t="n">
         <v>-81.30817852077075</v>
       </c>
-      <c r="X25" s="4" t="n">
+      <c r="Y25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Y25" s="5" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I4); 2 pathogen-host sp.; 30 spp. observed (17 bird / 13 amphibian); 1,787 EPA FRS facilities; adult asthma 8.1%; contaminant samples in county: 0</t>
+      <c r="Z25" s="4" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I4); 2 pathogen-host sp.; 30 spp. observed (17 bird / 13 amphibian); 52 EPA PFAS facilities of 1,787 FRS records; adult asthma 8.1%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2882,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.2876055999294784</v>
+        <v>0.289860211792837</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>2</v>
@@ -2833,43 +2911,46 @@
         <v>14</v>
       </c>
       <c r="N26" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="O26" s="4" t="n">
         <v>2790</v>
       </c>
-      <c r="O26" s="4" t="n">
+      <c r="P26" s="4" t="n">
         <v>141</v>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="Q26" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="Q26" s="4" t="n">
+      <c r="R26" s="4" t="n">
         <v>36016</v>
       </c>
-      <c r="R26" s="4" t="n">
+      <c r="S26" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="S26" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U26" s="4" t="inlineStr">
+      <c r="U26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V26" s="4" t="n">
+      <c r="W26" s="4" t="n">
         <v>28.773993732448</v>
       </c>
-      <c r="W26" s="4" t="n">
+      <c r="X26" s="4" t="n">
         <v>-81.4040838957511</v>
       </c>
-      <c r="X26" s="4" t="n">
+      <c r="Y26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Y26" s="5" t="inlineStr">
-        <is>
-          <t>2 sentinel-capable sp. (best tier I4); 1 pathogen-host sp.; 38 spp. observed (24 bird / 14 amphibian); 2,790 EPA FRS facilities; adult asthma 8.0%; contaminant samples in county: 0</t>
+      <c r="Z26" s="4" t="inlineStr">
+        <is>
+          <t>2 sentinel-capable sp. (best tier I4); 1 pathogen-host sp.; 38 spp. observed (24 bird / 14 amphibian); 77 EPA PFAS facilities of 2,790 FRS records; adult asthma 8.0%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2974,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2835791618489482</v>
+        <v>0.2894395927439818</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>1</v>
@@ -2922,43 +3003,46 @@
         <v>11</v>
       </c>
       <c r="N27" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="O27" s="4" t="n">
         <v>3073</v>
       </c>
-      <c r="O27" s="4" t="n">
+      <c r="P27" s="4" t="n">
         <v>145</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="Q27" s="4" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q27" s="4" t="n">
+      <c r="R27" s="4" t="n">
         <v>29859</v>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="S27" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="S27" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="T27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V27" s="4" t="n">
+      <c r="W27" s="4" t="n">
         <v>28.7402627039306</v>
       </c>
-      <c r="W27" s="4" t="n">
+      <c r="X27" s="4" t="n">
         <v>-80.77859334321759</v>
       </c>
-      <c r="X27" s="4" t="n">
+      <c r="Y27" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Y27" s="5" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 26 spp. observed (15 bird / 11 amphibian); 3,073 EPA FRS facilities; adult asthma 8.3%; contaminant samples in county: 0</t>
+      <c r="Z27" s="4" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 26 spp. observed (15 bird / 11 amphibian); 102 EPA PFAS facilities of 3,073 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -2968,12 +3052,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Escambia</t>
+          <t>Hendry</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2982,48 +3066,48 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2731948732987804</v>
+        <v>0.2836487457902339</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>I3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="J28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K28" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="K28" s="4" t="n">
-        <v>27</v>
-      </c>
       <c r="L28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="M28" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="M28" s="4" t="n">
-        <v>27</v>
-      </c>
       <c r="N28" s="4" t="n">
-        <v>2342</v>
+        <v>24</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>151</v>
+        <v>422</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>145</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>29166</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>9</v>
+        <v>20122</v>
       </c>
       <c r="S28" s="4" t="n">
         <v>0</v>
@@ -3031,23 +3115,26 @@
       <c r="T28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U28" s="4" t="inlineStr">
+      <c r="U28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V28" s="4" t="n">
-        <v>30.77900285928655</v>
-      </c>
       <c r="W28" s="4" t="n">
-        <v>-87.37585586179792</v>
+        <v>26.58712411433794</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y28" s="5" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I3); 0 pathogen-host sp.; 42 spp. observed (15 bird / 27 amphibian); 2,342 EPA FRS facilities; adult asthma 9.3%; contaminant samples in county: 0</t>
+        <v>-81.11355434266586</v>
+      </c>
+      <c r="Y28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z28" s="4" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I4); 2 pathogen-host sp.; 23 spp. observed (8 bird / 15 amphibian); 24 EPA PFAS facilities of 422 FRS records; adult asthma 8.8%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3057,12 +3144,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Hendry</t>
+          <t>Escambia</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -3071,72 +3158,75 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2595933046955196</v>
+        <v>0.2783411946719678</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>I3</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K29" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="L29" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="L29" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="M29" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>422</v>
+        <v>72</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>145</v>
+        <v>2342</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>151</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>20122</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0</v>
+        <v>29166</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U29" s="4" t="inlineStr">
+      <c r="U29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V29" s="4" t="n">
-        <v>26.58712411433794</v>
-      </c>
       <c r="W29" s="4" t="n">
-        <v>-81.11355434266586</v>
+        <v>30.77900285928655</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="5" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I4); 2 pathogen-host sp.; 23 spp. observed (8 bird / 15 amphibian); 422 EPA FRS facilities; adult asthma 8.8%; contaminant samples in county: 0</t>
+        <v>-87.37585586179792</v>
+      </c>
+      <c r="Y29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z29" s="4" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I3); 0 pathogen-host sp.; 42 spp. observed (15 bird / 27 amphibian); 72 EPA PFAS facilities of 2,342 FRS records; adult asthma 9.3%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3146,12 +3236,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>St. Johns</t>
+          <t>Okeechobee</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -3160,48 +3250,48 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.236868709021107</v>
+        <v>0.2587335256449427</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>I3</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="4" t="n">
         <v>26</v>
       </c>
       <c r="J30" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K30" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="K30" s="4" t="n">
+      <c r="L30" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="M30" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="M30" s="4" t="n">
-        <v>14</v>
-      </c>
       <c r="N30" s="4" t="n">
-        <v>1562</v>
+        <v>27</v>
       </c>
       <c r="O30" s="4" t="n">
+        <v>406</v>
+      </c>
+      <c r="P30" s="4" t="n">
         <v>141</v>
       </c>
-      <c r="P30" s="4" t="n">
-        <v>8.300000000000001</v>
-      </c>
       <c r="Q30" s="4" t="n">
-        <v>43433</v>
+        <v>8.9</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>4</v>
+        <v>23133</v>
       </c>
       <c r="S30" s="4" t="n">
         <v>0</v>
@@ -3209,23 +3299,26 @@
       <c r="T30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>repaired Saint-&gt;St.</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="n">
-        <v>29.84898480155067</v>
+      <c r="U30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-81.21699840343739</v>
+        <v>27.01700782445687</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y30" s="5" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I4); 1 pathogen-host sp.; 26 spp. observed (12 bird / 14 amphibian); 1,562 EPA FRS facilities; adult asthma 8.3%; contaminant samples in county: 0</t>
+        <v>-80.82670027712663</v>
+      </c>
+      <c r="Y30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z30" s="4" t="inlineStr">
+        <is>
+          <t>2 sentinel-capable sp. (best tier I3); 0 pathogen-host sp.; 26 spp. observed (14 bird / 12 amphibian); 27 EPA PFAS facilities of 406 FRS records; adult asthma 8.9%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3328,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Okeechobee</t>
+          <t>Dixie</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>12093</t>
+          <t>12029</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -3249,10 +3342,10 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.2312136559239019</v>
+        <v>0.2483963475253934</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
@@ -3260,37 +3353,37 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>406</v>
+        <v>8</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.9</v>
+        <v>140</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>23133</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0</v>
+        <v>19911</v>
       </c>
       <c r="S31" s="4" t="n">
         <v>0</v>
@@ -3298,23 +3391,26 @@
       <c r="T31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="4" t="inlineStr">
+      <c r="U31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V31" s="4" t="n">
-        <v>27.01700782445687</v>
-      </c>
       <c r="W31" s="4" t="n">
-        <v>-80.82670027712663</v>
+        <v>29.45565233248205</v>
       </c>
       <c r="X31" s="4" t="n">
+        <v>-83.3660880353189</v>
+      </c>
+      <c r="Y31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Y31" s="5" t="inlineStr">
-        <is>
-          <t>2 sentinel-capable sp. (best tier I3); 0 pathogen-host sp.; 26 spp. observed (14 bird / 12 amphibian); 406 EPA FRS facilities; adult asthma 8.9%; contaminant samples in county: 0</t>
+      <c r="Z31" s="4" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I3); 1 pathogen-host sp.; 7 spp. observed (3 bird / 4 amphibian); 8 EPA PFAS facilities of 110 FRS records; adult asthma 9.8%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3420,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Dixie</t>
+          <t>St. Johns</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -3338,72 +3434,75 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2145497438961852</v>
+        <v>0.2389521125126416</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>I3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
         <v>1</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K32" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="M32" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>1562</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q32" s="4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S32" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L32" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M32" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="N32" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="O32" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="P32" s="4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q32" s="4" t="n">
-        <v>19911</v>
-      </c>
-      <c r="R32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="T32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U32" s="4" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="V32" s="4" t="n">
-        <v>29.45565233248205</v>
+      <c r="U32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>repaired Saint-&gt;St.</t>
+        </is>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-83.3660880353189</v>
+        <v>29.84898480155067</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="5" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I3); 1 pathogen-host sp.; 7 spp. observed (3 bird / 4 amphibian); 110 EPA FRS facilities; adult asthma 9.8%; contaminant samples in county: 0</t>
+        <v>-81.21699840343739</v>
+      </c>
+      <c r="Y32" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z32" s="4" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I4); 1 pathogen-host sp.; 26 spp. observed (12 bird / 14 amphibian); 39 EPA PFAS facilities of 1,562 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3413,12 +3512,12 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>Putnam</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -3427,7 +3526,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.1808098860525509</v>
+        <v>0.1887561617920004</v>
       </c>
       <c r="F33" s="4" t="n">
         <v>0</v>
@@ -3441,58 +3540,61 @@
         <v>1</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2128</v>
+        <v>28</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>145</v>
+        <v>543</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>148</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>29426</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R33" s="4" t="n">
+        <v>22257</v>
+      </c>
+      <c r="S33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>29.64367220657317</v>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>-81.78027808142588</v>
+      </c>
+      <c r="Y33" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="S33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="4" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="V33" s="4" t="n">
-        <v>28.62392183557449</v>
-      </c>
-      <c r="W33" s="4" t="n">
-        <v>-81.79124705895957</v>
-      </c>
-      <c r="X33" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y33" s="5" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 29 spp. observed (14 bird / 15 amphibian); 2,128 EPA FRS facilities; adult asthma 8.3%; contaminant samples in county: 0</t>
+      <c r="Z33" s="4" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 26 spp. observed (9 bird / 17 amphibian); 28 EPA PFAS facilities of 543 FRS records; adult asthma 9.7%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3502,12 +3604,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Putnam</t>
+          <t>Lake</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -3516,7 +3618,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1676413828211134</v>
+        <v>0.1837148296142798</v>
       </c>
       <c r="F34" s="4" t="n">
         <v>0</v>
@@ -3530,58 +3632,61 @@
         <v>1</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>543</v>
+        <v>58</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>148</v>
+        <v>2128</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>145</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>22257</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0</v>
+        <v>29426</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U34" s="4" t="inlineStr">
+      <c r="U34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V34" s="4" t="n">
-        <v>29.64367220657317</v>
-      </c>
       <c r="W34" s="4" t="n">
-        <v>-81.78027808142588</v>
+        <v>28.62392183557449</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y34" s="5" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 26 spp. observed (9 bird / 17 amphibian); 543 EPA FRS facilities; adult asthma 9.7%; contaminant samples in county: 0</t>
+        <v>-81.79124705895957</v>
+      </c>
+      <c r="Y34" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z34" s="4" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 29 spp. observed (14 bird / 15 amphibian); 58 EPA PFAS facilities of 2,128 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3696,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Jackson</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -3605,7 +3710,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1582426826891931</v>
+        <v>0.1828401667218455</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>0</v>
@@ -3619,34 +3724,34 @@
         <v>1</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>1184</v>
+        <v>23</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>142</v>
+        <v>381</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>7.9</v>
+        <v>146</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>43758</v>
+        <v>9.6</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>2</v>
+        <v>21058</v>
       </c>
       <c r="S35" s="4" t="n">
         <v>0</v>
@@ -3654,23 +3759,26 @@
       <c r="T35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U35" s="4" t="inlineStr">
+      <c r="U35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V35" s="4" t="n">
-        <v>26.97300700137653</v>
-      </c>
       <c r="W35" s="4" t="n">
-        <v>-80.46357061141781</v>
+        <v>30.85166845762893</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y35" s="5" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 28 spp. observed (15 bird / 13 amphibian); 1,184 EPA FRS facilities; adult asthma 7.9%; contaminant samples in county: 0</t>
+        <v>-85.11492966299454</v>
+      </c>
+      <c r="Y35" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="4" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 26 spp. observed (1 bird / 25 amphibian); 23 EPA PFAS facilities of 381 FRS records; adult asthma 9.6%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3788,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Jackson</t>
+          <t>Franklin</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -3694,48 +3802,48 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.1571677379664856</v>
+        <v>0.1701431539693591</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>381</v>
+        <v>6</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>9.6</v>
+        <v>140</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>21058</v>
+        <v>8.9</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>0</v>
+        <v>26211</v>
       </c>
       <c r="S36" s="4" t="n">
         <v>0</v>
@@ -3743,23 +3851,26 @@
       <c r="T36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="4" t="inlineStr">
+      <c r="U36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V36" s="4" t="n">
-        <v>30.85166845762893</v>
-      </c>
       <c r="W36" s="4" t="n">
-        <v>-85.11492966299454</v>
+        <v>29.96571430542564</v>
       </c>
       <c r="X36" s="4" t="n">
+        <v>-84.70126741314157</v>
+      </c>
+      <c r="Y36" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Y36" s="5" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 26 spp. observed (1 bird / 25 amphibian); 381 EPA FRS facilities; adult asthma 9.6%; contaminant samples in county: 0</t>
+      <c r="Z36" s="4" t="inlineStr">
+        <is>
+          <t>1 sentinel-capable sp. (best tier I4); 0 pathogen-host sp.; 35 spp. observed (13 bird / 22 amphibian); 6 EPA PFAS facilities of 142 FRS records; adult asthma 8.9%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3880,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Franklin</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -3783,72 +3894,75 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.1487326568045033</v>
+        <v>0.1682338667052238</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J37" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K37" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="K37" s="4" t="n">
-        <v>22</v>
-      </c>
       <c r="L37" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="M37" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="M37" s="4" t="n">
-        <v>22</v>
-      </c>
       <c r="N37" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>1184</v>
+      </c>
+      <c r="P37" s="4" t="n">
         <v>142</v>
       </c>
-      <c r="O37" s="4" t="n">
-        <v>140</v>
-      </c>
-      <c r="P37" s="4" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Q37" s="4" t="n">
-        <v>26211</v>
+        <v>7.9</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>0</v>
+        <v>43758</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U37" s="4" t="inlineStr">
+      <c r="U37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V37" s="4" t="n">
-        <v>29.96571430542564</v>
-      </c>
       <c r="W37" s="4" t="n">
-        <v>-84.70126741314157</v>
+        <v>26.97300700137653</v>
       </c>
       <c r="X37" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y37" s="5" t="inlineStr">
-        <is>
-          <t>1 sentinel-capable sp. (best tier I4); 0 pathogen-host sp.; 35 spp. observed (13 bird / 22 amphibian); 142 EPA FRS facilities; adult asthma 8.9%; contaminant samples in county: 0</t>
+        <v>-80.46357061141781</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z37" s="4" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 28 spp. observed (15 bird / 13 amphibian); 41 EPA PFAS facilities of 1,184 FRS records; adult asthma 7.9%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3858,12 +3972,12 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Monroe</t>
+          <t>Jefferson</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>12065</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -3872,7 +3986,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.1326569562171862</v>
+        <v>0.1467564225494236</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>0</v>
@@ -3883,37 +3997,37 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>988</v>
+        <v>7</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>7.5</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>47382</v>
+        <v>9.6</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>1</v>
+        <v>25795</v>
       </c>
       <c r="S38" s="4" t="n">
         <v>0</v>
@@ -3921,23 +4035,26 @@
       <c r="T38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U38" s="4" t="inlineStr">
+      <c r="U38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V38" s="4" t="n">
-        <v>25.13947963570052</v>
-      </c>
       <c r="W38" s="4" t="n">
-        <v>-81.6540785876179</v>
+        <v>30.19800765490457</v>
       </c>
       <c r="X38" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y38" s="5" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 58 spp. observed (45 bird / 13 amphibian); 988 EPA FRS facilities; adult asthma 7.5%; contaminant samples in county: 0</t>
+        <v>-84.02905852163313</v>
+      </c>
+      <c r="Y38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z38" s="4" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 17 spp. observed (1 bird / 16 amphibian); 7 EPA PFAS facilities of 114 FRS records; adult asthma 9.6%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -3947,12 +4064,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Okaloosa</t>
+          <t>Monroe</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -3961,7 +4078,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.1226056498169964</v>
+        <v>0.1454978869715306</v>
       </c>
       <c r="F39" s="4" t="n">
         <v>0</v>
@@ -3975,58 +4092,61 @@
         <v>0</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>1238</v>
+        <v>38</v>
       </c>
       <c r="O39" s="4" t="n">
+        <v>988</v>
+      </c>
+      <c r="P39" s="4" t="n">
         <v>141</v>
       </c>
-      <c r="P39" s="4" t="n">
-        <v>8.6</v>
-      </c>
       <c r="Q39" s="4" t="n">
-        <v>34357</v>
+        <v>7.5</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>3</v>
+        <v>47382</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U39" s="4" t="inlineStr">
+      <c r="U39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V39" s="4" t="n">
-        <v>30.76545882256282</v>
-      </c>
       <c r="W39" s="4" t="n">
-        <v>-86.7600696602539</v>
+        <v>25.13947963570052</v>
       </c>
       <c r="X39" s="4" t="n">
+        <v>-81.6540785876179</v>
+      </c>
+      <c r="Y39" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Y39" s="5" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 29 spp. observed (8 bird / 21 amphibian); 1,238 EPA FRS facilities; adult asthma 8.6%; contaminant samples in county: 0</t>
+      <c r="Z39" s="4" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 58 spp. observed (45 bird / 13 amphibian); 38 EPA PFAS facilities of 988 FRS records; adult asthma 7.5%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4156,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Gadsden</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -4050,7 +4170,7 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.1176761095189886</v>
+        <v>0.1417015162117944</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>0</v>
@@ -4064,34 +4184,34 @@
         <v>0</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J40" s="6" t="n">
         <v>4</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L40" s="6" t="n">
         <v>4</v>
       </c>
       <c r="M40" s="6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1617</v>
+        <v>27</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>143</v>
+        <v>402</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>8.9</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>30774</v>
+        <v>10.4</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>2</v>
+        <v>21087</v>
       </c>
       <c r="S40" s="6" t="n">
         <v>0</v>
@@ -4099,23 +4219,26 @@
       <c r="T40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U40" s="6" t="inlineStr">
+      <c r="U40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V40" s="6" t="n">
-        <v>30.06380432335288</v>
-      </c>
       <c r="W40" s="6" t="n">
-        <v>-85.59707056676258</v>
+        <v>30.54571566514775</v>
       </c>
       <c r="X40" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y40" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 15 spp. observed (4 bird / 11 amphibian); 1,617 EPA FRS facilities; adult asthma 8.9%; contaminant samples in county: 0</t>
+        <v>-84.53430424051304</v>
+      </c>
+      <c r="Y40" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z40" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 19 spp. observed (4 bird / 15 amphibian); 27 EPA PFAS facilities of 402 FRS records; adult asthma 10.4%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4125,12 +4248,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Indian River</t>
+          <t>Okaloosa</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -4139,7 +4262,7 @@
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.1168406505981451</v>
+        <v>0.1381394543807041</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>0</v>
@@ -4153,58 +4276,61 @@
         <v>0</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M41" s="6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1435</v>
+        <v>56</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>143</v>
+        <v>1238</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>8.4</v>
+        <v>141</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>38274</v>
+        <v>8.6</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>4</v>
+        <v>34357</v>
       </c>
       <c r="S41" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U41" s="6" t="inlineStr">
+      <c r="U41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V41" s="6" t="n">
-        <v>27.67141007273313</v>
-      </c>
       <c r="W41" s="6" t="n">
-        <v>-80.63046059303447</v>
+        <v>30.76545882256282</v>
       </c>
       <c r="X41" s="6" t="n">
+        <v>-86.7600696602539</v>
+      </c>
+      <c r="Y41" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Y41" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 24 spp. observed (14 bird / 10 amphibian); 1,435 EPA FRS facilities; adult asthma 8.4%; contaminant samples in county: 0</t>
+      <c r="Z41" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 29 spp. observed (8 bird / 21 amphibian); 56 EPA PFAS facilities of 1,238 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4340,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Jefferson</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -4228,7 +4354,7 @@
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0.1166373864559414</v>
+        <v>0.1304363398898679</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>0</v>
@@ -4239,61 +4365,64 @@
         </is>
       </c>
       <c r="H42" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M42" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>140</v>
+        <v>1617</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>9.6</v>
+        <v>143</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>25795</v>
+        <v>8.9</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>0</v>
+        <v>30774</v>
       </c>
       <c r="S42" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U42" s="6" t="inlineStr">
+      <c r="U42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V42" s="6" t="n">
-        <v>30.19800765490457</v>
-      </c>
       <c r="W42" s="6" t="n">
-        <v>-84.02905852163313</v>
+        <v>30.06380432335288</v>
       </c>
       <c r="X42" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y42" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 17 spp. observed (1 bird / 16 amphibian); 114 EPA FRS facilities; adult asthma 9.6%; contaminant samples in county: 0</t>
+        <v>-85.59707056676258</v>
+      </c>
+      <c r="Y42" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z42" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 15 spp. observed (4 bird / 11 amphibian); 67 EPA PFAS facilities of 1,617 FRS records; adult asthma 8.9%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4303,12 +4432,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Liberty</t>
+          <t>Levy</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -4317,7 +4446,7 @@
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.1144289781714647</v>
+        <v>0.1293148925965684</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>0</v>
@@ -4328,37 +4457,37 @@
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M43" s="6" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>145</v>
+        <v>326</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>9.300000000000001</v>
+        <v>141</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>19585</v>
+        <v>9.5</v>
       </c>
       <c r="R43" s="6" t="n">
-        <v>0</v>
+        <v>22772</v>
       </c>
       <c r="S43" s="6" t="n">
         <v>0</v>
@@ -4366,23 +4495,26 @@
       <c r="T43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U43" s="6" t="inlineStr">
+      <c r="U43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V43" s="6" t="n">
-        <v>30.38733255651748</v>
-      </c>
       <c r="W43" s="6" t="n">
-        <v>-84.87934954093932</v>
+        <v>29.1524113491336</v>
       </c>
       <c r="X43" s="6" t="n">
+        <v>-82.94070012870873</v>
+      </c>
+      <c r="Y43" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y43" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 29 spp. observed (2 bird / 27 amphibian); 72 EPA FRS facilities; adult asthma 9.3%; contaminant samples in county: 0</t>
+      <c r="Z43" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 23 spp. observed (7 bird / 16 amphibian); 25 EPA PFAS facilities of 326 FRS records; adult asthma 9.5%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4392,12 +4524,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Gadsden</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -4406,7 +4538,7 @@
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.1139371444936071</v>
+        <v>0.1245584433494478</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>0</v>
@@ -4420,34 +4552,34 @@
         <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M44" s="6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>402</v>
+        <v>35</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>146</v>
+        <v>426</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>10.4</v>
+        <v>142</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>21087</v>
+        <v>9.5</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>0</v>
+        <v>19375</v>
       </c>
       <c r="S44" s="6" t="n">
         <v>0</v>
@@ -4455,23 +4587,26 @@
       <c r="T44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U44" s="6" t="inlineStr">
+      <c r="U44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V44" s="6" t="n">
-        <v>30.54571566514775</v>
-      </c>
       <c r="W44" s="6" t="n">
-        <v>-84.53430424051304</v>
+        <v>30.68708643605398</v>
       </c>
       <c r="X44" s="6" t="n">
+        <v>-85.65498721979255</v>
+      </c>
+      <c r="Y44" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y44" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 19 spp. observed (4 bird / 15 amphibian); 402 EPA FRS facilities; adult asthma 10.4%; contaminant samples in county: 0</t>
+      <c r="Z44" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 13 spp. observed (1 bird / 12 amphibian); 35 EPA PFAS facilities of 426 FRS records; adult asthma 9.5%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4616,12 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>St. Lucie</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>12111</t>
+          <t>12077</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -4495,7 +4630,7 @@
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0.104415220477789</v>
+        <v>0.1144289781714647</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>0</v>
@@ -4506,37 +4641,37 @@
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M45" s="6" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>1706</v>
+        <v>1</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>8.4</v>
+        <v>145</v>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>28426</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="R45" s="6" t="n">
-        <v>2</v>
+        <v>19585</v>
       </c>
       <c r="S45" s="6" t="n">
         <v>0</v>
@@ -4544,23 +4679,26 @@
       <c r="T45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U45" s="6" t="inlineStr">
-        <is>
-          <t>repaired Saint-&gt;St.</t>
-        </is>
-      </c>
-      <c r="V45" s="6" t="n">
-        <v>27.44682143438291</v>
+      <c r="U45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="6" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
       </c>
       <c r="W45" s="6" t="n">
-        <v>-80.51948770224774</v>
+        <v>30.38733255651748</v>
       </c>
       <c r="X45" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y45" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 10 spp. observed (4 bird / 6 amphibian); 1,706 EPA FRS facilities; adult asthma 8.4%; contaminant samples in county: 0</t>
+        <v>-84.87934954093932</v>
+      </c>
+      <c r="Y45" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 29 spp. observed (2 bird / 27 amphibian); 1 EPA PFAS facilities of 72 FRS records; adult asthma 9.3%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4570,12 +4708,12 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Levy</t>
+          <t>Columbia</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12023</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -4584,7 +4722,7 @@
         </is>
       </c>
       <c r="E46" s="6" t="n">
-        <v>0.09801569660288641</v>
+        <v>0.1114255118527624</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>0</v>
@@ -4598,34 +4736,34 @@
         <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L46" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M46" s="6" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="N46" s="6" t="n">
-        <v>326</v>
+        <v>17</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>141</v>
+        <v>434</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>9.5</v>
+        <v>143</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>22772</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>0</v>
+        <v>24569</v>
       </c>
       <c r="S46" s="6" t="n">
         <v>0</v>
@@ -4633,23 +4771,26 @@
       <c r="T46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U46" s="6" t="inlineStr">
+      <c r="U46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V46" s="6" t="n">
-        <v>29.1524113491336</v>
-      </c>
       <c r="W46" s="6" t="n">
-        <v>-82.94070012870873</v>
+        <v>30.26974293797891</v>
       </c>
       <c r="X46" s="6" t="n">
+        <v>-82.58522833564639</v>
+      </c>
+      <c r="Y46" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y46" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 23 spp. observed (7 bird / 16 amphibian); 326 EPA FRS facilities; adult asthma 9.5%; contaminant samples in county: 0</t>
+      <c r="Z46" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 12 spp. observed (3 bird / 9 amphibian); 17 EPA PFAS facilities of 434 FRS records; adult asthma 9.7%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4659,12 +4800,12 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Walton</t>
+          <t>St. Lucie</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -4673,7 +4814,7 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>0.095413737164578</v>
+        <v>0.1104514019531773</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>0</v>
@@ -4687,58 +4828,61 @@
         <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J47" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K47" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="K47" s="6" t="n">
-        <v>11</v>
-      </c>
       <c r="L47" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="M47" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="M47" s="6" t="n">
-        <v>11</v>
-      </c>
       <c r="N47" s="6" t="n">
-        <v>788</v>
+        <v>52</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>141</v>
+        <v>1706</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>8.5</v>
+        <v>143</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>35996</v>
+        <v>8.4</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>1</v>
+        <v>28426</v>
       </c>
       <c r="S47" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="6" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="V47" s="6" t="n">
-        <v>30.2401971508469</v>
+      <c r="U47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="6" t="inlineStr">
+        <is>
+          <t>repaired Saint-&gt;St.</t>
+        </is>
       </c>
       <c r="W47" s="6" t="n">
-        <v>-86.32236411121448</v>
+        <v>27.44682143438291</v>
       </c>
       <c r="X47" s="6" t="n">
+        <v>-80.51948770224774</v>
+      </c>
+      <c r="Y47" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Y47" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 17 spp. observed (6 bird / 11 amphibian); 788 EPA FRS facilities; adult asthma 8.5%; contaminant samples in county: 0</t>
+      <c r="Z47" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 10 spp. observed (4 bird / 6 amphibian); 52 EPA PFAS facilities of 1,706 FRS records; adult asthma 8.4%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4748,12 +4892,12 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Columbia</t>
+          <t>Indian River</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -4762,7 +4906,7 @@
         </is>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0.0954109672662683</v>
+        <v>0.1097651904485143</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>0</v>
@@ -4776,58 +4920,61 @@
         <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M48" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N48" s="6" t="n">
-        <v>434</v>
+        <v>23</v>
       </c>
       <c r="O48" s="6" t="n">
+        <v>1435</v>
+      </c>
+      <c r="P48" s="6" t="n">
         <v>143</v>
       </c>
-      <c r="P48" s="6" t="n">
-        <v>9.699999999999999</v>
-      </c>
       <c r="Q48" s="6" t="n">
-        <v>24569</v>
+        <v>8.4</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>0</v>
+        <v>38274</v>
       </c>
       <c r="S48" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="U48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V48" s="6" t="n">
-        <v>30.26974293797891</v>
-      </c>
       <c r="W48" s="6" t="n">
-        <v>-82.58522833564639</v>
+        <v>27.67141007273313</v>
       </c>
       <c r="X48" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 12 spp. observed (3 bird / 9 amphibian); 434 EPA FRS facilities; adult asthma 9.7%; contaminant samples in county: 0</t>
+        <v>-80.63046059303447</v>
+      </c>
+      <c r="Y48" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z48" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 24 spp. observed (14 bird / 10 amphibian); 23 EPA PFAS facilities of 1,435 FRS records; adult asthma 8.4%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4837,12 +4984,12 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Nassau</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -4851,7 +4998,7 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0.0926959061442082</v>
+        <v>0.1056950295912198</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>0</v>
@@ -4865,34 +5012,34 @@
         <v>0</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M49" s="6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="N49" s="6" t="n">
-        <v>426</v>
+        <v>29</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>142</v>
+        <v>616</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>9.5</v>
+        <v>146</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>19375</v>
+        <v>8.5</v>
       </c>
       <c r="R49" s="6" t="n">
-        <v>0</v>
+        <v>37787</v>
       </c>
       <c r="S49" s="6" t="n">
         <v>0</v>
@@ -4900,23 +5047,26 @@
       <c r="T49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U49" s="6" t="inlineStr">
+      <c r="U49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V49" s="6" t="n">
-        <v>30.68708643605398</v>
-      </c>
       <c r="W49" s="6" t="n">
-        <v>-85.65498721979255</v>
+        <v>30.49246958955147</v>
       </c>
       <c r="X49" s="6" t="n">
+        <v>-81.53918408848806</v>
+      </c>
+      <c r="Y49" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y49" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 13 spp. observed (1 bird / 12 amphibian); 426 EPA FRS facilities; adult asthma 9.5%; contaminant samples in county: 0</t>
+      <c r="Z49" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 15 spp. observed (8 bird / 7 amphibian); 29 EPA PFAS facilities of 616 FRS records; adult asthma 8.5%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -4926,12 +5076,12 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Nassau</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -4940,7 +5090,7 @@
         </is>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0.0869473676305158</v>
+        <v>0.0997485032154499</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>0</v>
@@ -4954,34 +5104,34 @@
         <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="J50" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="K50" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="L50" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="M50" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N50" s="6" t="n">
-        <v>616</v>
-      </c>
       <c r="O50" s="6" t="n">
-        <v>146</v>
+        <v>210</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>8.5</v>
+        <v>147</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>37787</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R50" s="6" t="n">
-        <v>0</v>
+        <v>19492</v>
       </c>
       <c r="S50" s="6" t="n">
         <v>0</v>
@@ -4989,23 +5139,26 @@
       <c r="T50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="6" t="inlineStr">
+      <c r="U50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V50" s="6" t="n">
-        <v>30.49246958955147</v>
-      </c>
       <c r="W50" s="6" t="n">
-        <v>-81.53918408848806</v>
+        <v>29.86777249166445</v>
       </c>
       <c r="X50" s="6" t="n">
+        <v>-83.38071940996305</v>
+      </c>
+      <c r="Y50" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y50" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 15 spp. observed (8 bird / 7 amphibian); 616 EPA FRS facilities; adult asthma 8.5%; contaminant samples in county: 0</t>
+      <c r="Z50" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 3 spp. observed (2 bird / 1 amphibian); 15 EPA PFAS facilities of 210 FRS records; adult asthma 9.8%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5015,12 +5168,12 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Flagler</t>
+          <t>Walton</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>12035</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -5029,7 +5182,7 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0.0781537857935985</v>
+        <v>0.09906935553436121</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>0</v>
@@ -5043,58 +5196,61 @@
         <v>0</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K51" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L51" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="L51" s="6" t="n">
-        <v>2</v>
-      </c>
       <c r="M51" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>788</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v>35996</v>
+      </c>
+      <c r="S51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="6" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
+      </c>
+      <c r="W51" s="6" t="n">
+        <v>30.2401971508469</v>
+      </c>
+      <c r="X51" s="6" t="n">
+        <v>-86.32236411121448</v>
+      </c>
+      <c r="Y51" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="N51" s="6" t="n">
-        <v>605</v>
-      </c>
-      <c r="O51" s="6" t="n">
-        <v>142</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v>32722</v>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="6" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="V51" s="6" t="n">
-        <v>29.44175296054901</v>
-      </c>
-      <c r="W51" s="6" t="n">
-        <v>-81.37840920315203</v>
-      </c>
-      <c r="X51" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y51" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 8 spp. observed (2 bird / 6 amphibian); 605 EPA FRS facilities; adult asthma 8.5%; contaminant samples in county: 0</t>
+      <c r="Z51" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 17 spp. observed (6 bird / 11 amphibian); 19 EPA PFAS facilities of 788 FRS records; adult asthma 8.5%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5274,7 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0.0723958493343204</v>
+        <v>0.0954924908632324</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>0</v>
@@ -5147,43 +5303,46 @@
         <v>11</v>
       </c>
       <c r="N52" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O52" s="6" t="n">
         <v>170</v>
       </c>
-      <c r="O52" s="6" t="n">
+      <c r="P52" s="6" t="n">
         <v>141</v>
       </c>
-      <c r="P52" s="6" t="n">
+      <c r="Q52" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="Q52" s="6" t="n">
+      <c r="R52" s="6" t="n">
         <v>27626</v>
       </c>
-      <c r="R52" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="S52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="6" t="inlineStr">
+      <c r="U52" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V52" s="6" t="n">
+      <c r="W52" s="6" t="n">
         <v>29.80367220010124</v>
       </c>
-      <c r="W52" s="6" t="n">
+      <c r="X52" s="6" t="n">
         <v>-85.19096920056063</v>
       </c>
-      <c r="X52" s="6" t="n">
+      <c r="Y52" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y52" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 15 spp. observed (4 bird / 11 amphibian); 170 EPA FRS facilities; adult asthma 9.5%; contaminant samples in county: 0</t>
+      <c r="Z52" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 15 spp. observed (4 bird / 11 amphibian); 8 EPA PFAS facilities of 170 FRS records; adult asthma 9.5%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5193,12 +5352,12 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Sumter</t>
+          <t>Suwannee</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>12119</t>
+          <t>12121</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -5207,7 +5366,7 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>0.0690333026258627</v>
+        <v>0.0939500948127851</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>0</v>
@@ -5221,34 +5380,34 @@
         <v>0</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="K53" s="6" t="n">
-        <v>7</v>
-      </c>
       <c r="L53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="M53" s="6" t="n">
-        <v>7</v>
-      </c>
       <c r="N53" s="6" t="n">
-        <v>550</v>
+        <v>18</v>
       </c>
       <c r="O53" s="6" t="n">
+        <v>303</v>
+      </c>
+      <c r="P53" s="6" t="n">
         <v>142</v>
       </c>
-      <c r="P53" s="6" t="n">
-        <v>7.9</v>
-      </c>
       <c r="Q53" s="6" t="n">
-        <v>35879</v>
+        <v>9.1</v>
       </c>
       <c r="R53" s="6" t="n">
-        <v>1</v>
+        <v>23389</v>
       </c>
       <c r="S53" s="6" t="n">
         <v>0</v>
@@ -5256,23 +5415,26 @@
       <c r="T53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U53" s="6" t="inlineStr">
+      <c r="U53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V53" s="6" t="n">
-        <v>28.53545531224325</v>
-      </c>
       <c r="W53" s="6" t="n">
-        <v>-82.1186953043933</v>
+        <v>30.01770471466019</v>
       </c>
       <c r="X53" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y53" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 11 spp. observed (4 bird / 7 amphibian); 550 EPA FRS facilities; adult asthma 7.9%; contaminant samples in county: 0</t>
+        <v>-82.79762265632753</v>
+      </c>
+      <c r="Y53" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z53" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 5 spp. observed (1 bird / 4 amphibian); 18 EPA PFAS facilities of 303 FRS records; adult asthma 9.1%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5444,12 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -5296,7 +5458,7 @@
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0.0684745089304452</v>
+        <v>0.0936373424712498</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>0</v>
@@ -5310,34 +5472,34 @@
         <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="K54" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="L54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M54" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="N54" s="6" t="n">
-        <v>210</v>
+        <v>14</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>143</v>
       </c>
       <c r="Q54" s="6" t="n">
-        <v>19492</v>
+        <v>9.6</v>
       </c>
       <c r="R54" s="6" t="n">
-        <v>0</v>
+        <v>18909</v>
       </c>
       <c r="S54" s="6" t="n">
         <v>0</v>
@@ -5345,23 +5507,26 @@
       <c r="T54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U54" s="6" t="inlineStr">
+      <c r="U54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V54" s="6" t="n">
-        <v>29.86777249166445</v>
-      </c>
       <c r="W54" s="6" t="n">
-        <v>-83.38071940996305</v>
+        <v>30.43237542370881</v>
       </c>
       <c r="X54" s="6" t="n">
+        <v>-83.48353451957558</v>
+      </c>
+      <c r="Y54" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y54" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 3 spp. observed (2 bird / 1 amphibian); 210 EPA FRS facilities; adult asthma 9.8%; contaminant samples in county: 0</t>
+      <c r="Z54" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 2 spp. observed (0 bird / 2 amphibian); 14 EPA PFAS facilities of 166 FRS records; adult asthma 9.6%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5536,12 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Suwannee</t>
+          <t>Holmes</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -5385,7 +5550,7 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0.06784449235372721</v>
+        <v>0.09165000374258821</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>0</v>
@@ -5399,58 +5564,61 @@
         <v>0</v>
       </c>
       <c r="I55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>126</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>19028</v>
+      </c>
+      <c r="S55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="6" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
+      </c>
+      <c r="W55" s="6" t="n">
+        <v>30.8589109524587</v>
+      </c>
+      <c r="X55" s="6" t="n">
+        <v>-85.8772468924296</v>
+      </c>
+      <c r="Y55" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="J55" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>303</v>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>142</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>23389</v>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="6" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="V55" s="6" t="n">
-        <v>30.01770471466019</v>
-      </c>
-      <c r="W55" s="6" t="n">
-        <v>-82.79762265632753</v>
-      </c>
-      <c r="X55" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y55" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 5 spp. observed (1 bird / 4 amphibian); 303 EPA FRS facilities; adult asthma 9.1%; contaminant samples in county: 0</t>
+      <c r="Z55" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 1 spp. observed (0 bird / 1 amphibian); 9 EPA PFAS facilities of 126 FRS records; adult asthma 10.1%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5628,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Baker</t>
+          <t>Sumter</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -5474,7 +5642,7 @@
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>0.063471411140641</v>
+        <v>0.0913019951081713</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>0</v>
@@ -5488,58 +5656,61 @@
         <v>0</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M56" s="6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>140</v>
+        <v>550</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>9.300000000000001</v>
+        <v>142</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>24051</v>
+        <v>7.9</v>
       </c>
       <c r="R56" s="6" t="n">
-        <v>0</v>
+        <v>35879</v>
       </c>
       <c r="S56" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U56" s="6" t="inlineStr">
+      <c r="U56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V56" s="6" t="n">
-        <v>30.45721609635384</v>
-      </c>
       <c r="W56" s="6" t="n">
-        <v>-82.25650767548719</v>
+        <v>28.53545531224325</v>
       </c>
       <c r="X56" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y56" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 13 spp. observed (0 bird / 13 amphibian); 150 EPA FRS facilities; adult asthma 9.3%; contaminant samples in county: 0</t>
+        <v>-82.1186953043933</v>
+      </c>
+      <c r="Y56" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z56" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 11 spp. observed (4 bird / 7 amphibian); 30 EPA PFAS facilities of 550 FRS records; adult asthma 7.9%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5549,12 +5720,12 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>DeSoto</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -5563,7 +5734,7 @@
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>0.0603685220964213</v>
+        <v>0.0892697765323244</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>0</v>
@@ -5577,34 +5748,34 @@
         <v>0</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M57" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N57" s="6" t="n">
-        <v>263</v>
+        <v>8</v>
       </c>
       <c r="O57" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="P57" s="6" t="n">
         <v>141</v>
       </c>
-      <c r="P57" s="6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="Q57" s="6" t="n">
-        <v>18193</v>
+        <v>9.9</v>
       </c>
       <c r="R57" s="6" t="n">
-        <v>0</v>
+        <v>15532</v>
       </c>
       <c r="S57" s="6" t="n">
         <v>0</v>
@@ -5612,23 +5783,26 @@
       <c r="T57" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U57" s="6" t="inlineStr">
+      <c r="U57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V57" s="6" t="n">
-        <v>27.15938340081132</v>
-      </c>
       <c r="W57" s="6" t="n">
-        <v>-81.74374798691413</v>
+        <v>30.5237846237284</v>
       </c>
       <c r="X57" s="6" t="n">
+        <v>-82.96235429911742</v>
+      </c>
+      <c r="Y57" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y57" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 6 spp. observed (4 bird / 2 amphibian); 263 EPA FRS facilities; adult asthma 8.8%; contaminant samples in county: 0</t>
+      <c r="Z57" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 4 spp. observed (1 bird / 3 amphibian); 8 EPA PFAS facilities of 122 FRS records; adult asthma 9.9%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5638,12 +5812,12 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Holmes</t>
+          <t>DeSoto</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -5652,7 +5826,7 @@
         </is>
       </c>
       <c r="E58" s="6" t="n">
-        <v>0.0586470182687231</v>
+        <v>0.0887523071706998</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>0</v>
@@ -5666,34 +5840,34 @@
         <v>0</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M58" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N58" s="6" t="n">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="O58" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="P58" s="6" t="n">
         <v>141</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v>10.1</v>
-      </c>
       <c r="Q58" s="6" t="n">
-        <v>19028</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R58" s="6" t="n">
-        <v>0</v>
+        <v>18193</v>
       </c>
       <c r="S58" s="6" t="n">
         <v>0</v>
@@ -5701,23 +5875,26 @@
       <c r="T58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U58" s="6" t="inlineStr">
+      <c r="U58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V58" s="6" t="n">
-        <v>30.8589109524587</v>
-      </c>
       <c r="W58" s="6" t="n">
-        <v>-85.8772468924296</v>
+        <v>27.15938340081132</v>
       </c>
       <c r="X58" s="6" t="n">
+        <v>-81.74374798691413</v>
+      </c>
+      <c r="Y58" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y58" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 1 spp. observed (0 bird / 1 amphibian); 126 EPA FRS facilities; adult asthma 10.1%; contaminant samples in county: 0</t>
+      <c r="Z58" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 6 spp. observed (4 bird / 2 amphibian); 17 EPA PFAS facilities of 263 FRS records; adult asthma 8.8%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5904,12 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Gilchrist</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -5741,7 +5918,7 @@
         </is>
       </c>
       <c r="E59" s="6" t="n">
-        <v>0.0580274080457923</v>
+        <v>0.0855814286555671</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>0</v>
@@ -5755,34 +5932,34 @@
         <v>0</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L59" s="6" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N59" s="6" t="n">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>9.6</v>
+        <v>140</v>
       </c>
       <c r="Q59" s="6" t="n">
-        <v>18909</v>
+        <v>9.5</v>
       </c>
       <c r="R59" s="6" t="n">
-        <v>0</v>
+        <v>22775</v>
       </c>
       <c r="S59" s="6" t="n">
         <v>0</v>
@@ -5790,23 +5967,26 @@
       <c r="T59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U59" s="6" t="inlineStr">
+      <c r="U59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V59" s="6" t="n">
-        <v>30.43237542370881</v>
-      </c>
       <c r="W59" s="6" t="n">
-        <v>-83.48353451957558</v>
+        <v>29.70267721799804</v>
       </c>
       <c r="X59" s="6" t="n">
+        <v>-82.79035312255256</v>
+      </c>
+      <c r="Y59" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y59" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 2 spp. observed (0 bird / 2 amphibian); 166 EPA FRS facilities; adult asthma 9.6%; contaminant samples in county: 0</t>
+      <c r="Z59" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 1 spp. observed (0 bird / 1 amphibian); 11 EPA PFAS facilities of 123 FRS records; adult asthma 9.5%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5816,12 +5996,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Calhoun</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -5830,7 +6010,7 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>0.0579800581967518</v>
+        <v>0.0846300872597938</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>0</v>
@@ -5844,34 +6024,34 @@
         <v>0</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" s="6" t="n">
         <v>3</v>
       </c>
       <c r="L60" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="6" t="n">
         <v>3</v>
       </c>
       <c r="N60" s="6" t="n">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>9.9</v>
+        <v>140</v>
       </c>
       <c r="Q60" s="6" t="n">
-        <v>15532</v>
+        <v>9.1</v>
       </c>
       <c r="R60" s="6" t="n">
-        <v>0</v>
+        <v>19512</v>
       </c>
       <c r="S60" s="6" t="n">
         <v>0</v>
@@ -5879,23 +6059,26 @@
       <c r="T60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U60" s="6" t="inlineStr">
+      <c r="U60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V60" s="6" t="n">
-        <v>30.5237846237284</v>
-      </c>
       <c r="W60" s="6" t="n">
-        <v>-82.96235429911742</v>
+        <v>30.3946890531829</v>
       </c>
       <c r="X60" s="6" t="n">
+        <v>-85.27724460622655</v>
+      </c>
+      <c r="Y60" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y60" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 4 spp. observed (1 bird / 3 amphibian); 122 EPA FRS facilities; adult asthma 9.9%; contaminant samples in county: 0</t>
+      <c r="Z60" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 3 spp. observed (0 bird / 3 amphibian); 13 EPA PFAS facilities of 117 FRS records; adult asthma 9.1%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5905,12 +6088,12 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Glades</t>
+          <t>Baker</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -5919,7 +6102,7 @@
         </is>
       </c>
       <c r="E61" s="6" t="n">
-        <v>0.0570545384256269</v>
+        <v>0.083528446310678</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>0</v>
@@ -5933,58 +6116,61 @@
         <v>0</v>
       </c>
       <c r="I61" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="L61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="N61" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K61" s="6" t="n">
+      <c r="O61" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v>24051</v>
+      </c>
+      <c r="S61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="6" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
+      </c>
+      <c r="W61" s="6" t="n">
+        <v>30.45721609635384</v>
+      </c>
+      <c r="X61" s="6" t="n">
+        <v>-82.25650767548719</v>
+      </c>
+      <c r="Y61" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="L61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N61" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="O61" s="6" t="n">
-        <v>140</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v>22128</v>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="6" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="V61" s="6" t="n">
-        <v>26.99720319571579</v>
-      </c>
-      <c r="W61" s="6" t="n">
-        <v>-81.37816793850926</v>
-      </c>
-      <c r="X61" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y61" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 6 spp. observed (1 bird / 5 amphibian); 200 EPA FRS facilities; adult asthma 9.0%; contaminant samples in county: 0</t>
+      <c r="Z61" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 13 spp. observed (0 bird / 13 amphibian); 6 EPA PFAS facilities of 150 FRS records; adult asthma 9.3%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -5994,12 +6180,12 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Hardee</t>
+          <t>Glades</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -6008,7 +6194,7 @@
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>0.0545054067850056</v>
+        <v>0.0808930008294112</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>0</v>
@@ -6022,34 +6208,34 @@
         <v>0</v>
       </c>
       <c r="I62" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J62" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="K62" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="L62" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>203</v>
+        <v>10</v>
       </c>
       <c r="O62" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="P62" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="P62" s="6" t="n">
-        <v>8.9</v>
-      </c>
       <c r="Q62" s="6" t="n">
-        <v>20181</v>
+        <v>9</v>
       </c>
       <c r="R62" s="6" t="n">
-        <v>0</v>
+        <v>22128</v>
       </c>
       <c r="S62" s="6" t="n">
         <v>0</v>
@@ -6057,23 +6243,26 @@
       <c r="T62" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U62" s="6" t="inlineStr">
+      <c r="U62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V62" s="6" t="n">
-        <v>27.44650041645728</v>
-      </c>
       <c r="W62" s="6" t="n">
-        <v>-81.72937125003942</v>
+        <v>26.99720319571579</v>
       </c>
       <c r="X62" s="6" t="n">
+        <v>-81.37816793850926</v>
+      </c>
+      <c r="Y62" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y62" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 5 spp. observed (2 bird / 3 amphibian); 203 EPA FRS facilities; adult asthma 8.9%; contaminant samples in county: 0</t>
+      <c r="Z62" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 6 spp. observed (1 bird / 5 amphibian); 10 EPA PFAS facilities of 200 FRS records; adult asthma 9.0%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -6083,12 +6272,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Gilchrist</t>
+          <t>Flagler</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>12041</t>
+          <t>12035</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -6097,7 +6286,7 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>0.0477071136956218</v>
+        <v>0.0785428682888155</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>0</v>
@@ -6111,58 +6300,61 @@
         <v>0</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J63" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L63" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="O63" s="6" t="n">
-        <v>140</v>
+        <v>605</v>
       </c>
       <c r="P63" s="6" t="n">
-        <v>9.5</v>
+        <v>142</v>
       </c>
       <c r="Q63" s="6" t="n">
-        <v>22775</v>
+        <v>8.5</v>
       </c>
       <c r="R63" s="6" t="n">
-        <v>0</v>
+        <v>32722</v>
       </c>
       <c r="S63" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U63" s="6" t="inlineStr">
+      <c r="U63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V63" s="6" t="n">
-        <v>29.70267721799804</v>
-      </c>
       <c r="W63" s="6" t="n">
-        <v>-82.79035312255256</v>
+        <v>29.44175296054901</v>
       </c>
       <c r="X63" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y63" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 1 spp. observed (0 bird / 1 amphibian); 123 EPA FRS facilities; adult asthma 9.5%; contaminant samples in county: 0</t>
+        <v>-81.37840920315203</v>
+      </c>
+      <c r="Y63" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z63" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 8 spp. observed (2 bird / 6 amphibian); 12 EPA PFAS facilities of 605 FRS records; adult asthma 8.5%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -6172,12 +6364,12 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Calhoun</t>
+          <t>Hardee</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -6186,7 +6378,7 @@
         </is>
       </c>
       <c r="E64" s="6" t="n">
-        <v>0.0419609007427128</v>
+        <v>0.0757309907720093</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>0</v>
@@ -6200,34 +6392,34 @@
         <v>0</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" s="6" t="n">
         <v>3</v>
       </c>
       <c r="L64" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" s="6" t="n">
         <v>3</v>
       </c>
       <c r="N64" s="6" t="n">
-        <v>117</v>
+        <v>9</v>
       </c>
       <c r="O64" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="P64" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="P64" s="6" t="n">
-        <v>9.1</v>
-      </c>
       <c r="Q64" s="6" t="n">
-        <v>19512</v>
+        <v>8.9</v>
       </c>
       <c r="R64" s="6" t="n">
-        <v>0</v>
+        <v>20181</v>
       </c>
       <c r="S64" s="6" t="n">
         <v>0</v>
@@ -6235,23 +6427,26 @@
       <c r="T64" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U64" s="6" t="inlineStr">
+      <c r="U64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V64" s="6" t="n">
-        <v>30.3946890531829</v>
-      </c>
       <c r="W64" s="6" t="n">
-        <v>-85.27724460622655</v>
+        <v>27.44650041645728</v>
       </c>
       <c r="X64" s="6" t="n">
+        <v>-81.72937125003942</v>
+      </c>
+      <c r="Y64" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y64" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 3 spp. observed (0 bird / 3 amphibian); 117 EPA FRS facilities; adult asthma 9.1%; contaminant samples in county: 0</t>
+      <c r="Z64" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 5 spp. observed (2 bird / 3 amphibian); 9 EPA PFAS facilities of 203 FRS records; adult asthma 8.9%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6470,7 @@
         </is>
       </c>
       <c r="E65" s="6" t="n">
-        <v>0.0363992543887631</v>
+        <v>0.0671851274118558</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>0</v>
@@ -6304,48 +6499,51 @@
         <v>3</v>
       </c>
       <c r="N65" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="O65" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="O65" s="6" t="n">
+      <c r="P65" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="P65" s="6" t="n">
+      <c r="Q65" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q65" s="6" t="n">
+      <c r="R65" s="6" t="n">
         <v>17022</v>
       </c>
-      <c r="R65" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="S65" s="6" t="n">
         <v>0</v>
       </c>
       <c r="T65" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U65" s="6" t="inlineStr">
+      <c r="U65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
-      <c r="V65" s="6" t="n">
+      <c r="W65" s="6" t="n">
         <v>29.98566043741613</v>
       </c>
-      <c r="W65" s="6" t="n">
+      <c r="X65" s="6" t="n">
         <v>-83.05917885028005</v>
       </c>
-      <c r="X65" s="6" t="n">
+      <c r="Y65" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y65" s="7" t="inlineStr">
-        <is>
-          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 4 spp. observed (1 bird / 3 amphibian); 83 EPA FRS facilities; adult asthma 9.2%; contaminant samples in county: 0</t>
+      <c r="Z65" s="6" t="inlineStr">
+        <is>
+          <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 4 spp. observed (1 bird / 3 amphibian); 5 EPA PFAS facilities of 83 FRS records; adult asthma 9.2%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y65"/>
+  <autoFilter ref="A1:Z65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7863,7 +8061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7876,6 +8074,7 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7896,35 +8095,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>pfas_facilities</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>spoke_chemicals_found</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>spoke_sdoh_measures</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>adult_asthma_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>per_capita_income</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>cm_cities</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>rcms</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>climate_papers</t>
         </is>
@@ -7945,24 +8149,27 @@
         <v>1505</v>
       </c>
       <c r="D2" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="E2" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="F2" s="8" t="n">
         <v>1107</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="G2" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="G2" s="8" t="n">
+      <c r="H2" s="8" t="n">
         <v>29821</v>
       </c>
-      <c r="H2" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J2" s="8" t="n">
+      <c r="K2" s="8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7981,24 +8188,27 @@
         <v>150</v>
       </c>
       <c r="D3" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="F3" s="8" t="n">
         <v>951</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="G3" s="8" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="H3" s="8" t="n">
         <v>24051</v>
       </c>
-      <c r="H3" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8017,24 +8227,27 @@
         <v>1617</v>
       </c>
       <c r="D4" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="F4" s="8" t="n">
         <v>1109</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="G4" s="8" t="n">
         <v>8.9</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="H4" s="8" t="n">
         <v>30774</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="I4" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="J4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="K4" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8053,24 +8266,27 @@
         <v>203</v>
       </c>
       <c r="D5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="F5" s="8" t="n">
         <v>957</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="G5" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="H5" s="8" t="n">
         <v>21003</v>
       </c>
-      <c r="H5" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8089,24 +8305,27 @@
         <v>3929</v>
       </c>
       <c r="D6" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>149</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="F6" s="8" t="n">
         <v>1120</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="G6" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="H6" s="8" t="n">
         <v>33662</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="I6" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="J6" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="K6" s="8" t="n">
         <v>21</v>
       </c>
     </row>
@@ -8125,24 +8344,27 @@
         <v>7302</v>
       </c>
       <c r="D7" s="8" t="n">
+        <v>267</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="F7" s="8" t="n">
         <v>1140</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="G7" s="8" t="n">
         <v>7.8</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="H7" s="8" t="n">
         <v>34063</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="I7" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="J7" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="K7" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8161,24 +8383,27 @@
         <v>117</v>
       </c>
       <c r="D8" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="F8" s="8" t="n">
         <v>924</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="G8" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="H8" s="8" t="n">
         <v>19512</v>
       </c>
-      <c r="H8" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8197,24 +8422,27 @@
         <v>975</v>
       </c>
       <c r="D9" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="F9" s="8" t="n">
         <v>1072</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="G9" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="H9" s="8" t="n">
         <v>33275</v>
-      </c>
-      <c r="H9" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8233,24 +8461,27 @@
         <v>619</v>
       </c>
       <c r="D10" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="F10" s="8" t="n">
         <v>1086</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="G10" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="H10" s="8" t="n">
         <v>28174</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I10" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8269,24 +8500,27 @@
         <v>1155</v>
       </c>
       <c r="D11" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="E11" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="F11" s="8" t="n">
         <v>1080</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="G11" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="H11" s="8" t="n">
         <v>32037</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8305,24 +8539,27 @@
         <v>1900</v>
       </c>
       <c r="D12" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="E12" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="F12" s="8" t="n">
         <v>1097</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="G12" s="8" t="n">
         <v>7.6</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="H12" s="8" t="n">
         <v>46785</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="I12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="J12" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="8" t="n">
+      <c r="K12" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8341,24 +8578,27 @@
         <v>434</v>
       </c>
       <c r="D13" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="F13" s="8" t="n">
         <v>1040</v>
       </c>
-      <c r="F13" s="8" t="n">
+      <c r="G13" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="H13" s="8" t="n">
         <v>24569</v>
       </c>
-      <c r="H13" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I13" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8377,24 +8617,27 @@
         <v>263</v>
       </c>
       <c r="D14" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="F14" s="8" t="n">
         <v>975</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="G14" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="H14" s="8" t="n">
         <v>18193</v>
       </c>
-      <c r="H14" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8413,24 +8656,27 @@
         <v>110</v>
       </c>
       <c r="D15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="F15" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="G15" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="H15" s="8" t="n">
         <v>19911</v>
       </c>
-      <c r="H15" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I15" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8449,24 +8695,27 @@
         <v>7752</v>
       </c>
       <c r="D16" s="8" t="n">
+        <v>276</v>
+      </c>
+      <c r="E16" s="8" t="n">
         <v>149</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="F16" s="8" t="n">
         <v>1137</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="G16" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="H16" s="8" t="n">
         <v>32233</v>
       </c>
-      <c r="H16" s="8" t="n">
+      <c r="I16" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I16" s="8" t="n">
+      <c r="J16" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="8" t="n">
+      <c r="K16" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8485,24 +8734,27 @@
         <v>2342</v>
       </c>
       <c r="D17" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="E17" s="8" t="n">
         <v>151</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="F17" s="8" t="n">
         <v>1114</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="G17" s="8" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="H17" s="8" t="n">
         <v>29166</v>
       </c>
-      <c r="H17" s="8" t="n">
+      <c r="I17" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="I17" s="8" t="n">
+      <c r="J17" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="8" t="n">
+      <c r="K17" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8521,24 +8773,27 @@
         <v>605</v>
       </c>
       <c r="D18" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="F18" s="8" t="n">
         <v>1070</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="G18" s="8" t="n">
         <v>8.5</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="H18" s="8" t="n">
         <v>32722</v>
       </c>
-      <c r="H18" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I18" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="8" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8557,24 +8812,27 @@
         <v>142</v>
       </c>
       <c r="D19" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="F19" s="8" t="n">
         <v>906</v>
       </c>
-      <c r="F19" s="8" t="n">
+      <c r="G19" s="8" t="n">
         <v>8.9</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="H19" s="8" t="n">
         <v>26211</v>
       </c>
-      <c r="H19" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I19" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8593,24 +8851,27 @@
         <v>402</v>
       </c>
       <c r="D20" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E20" s="8" t="n">
         <v>146</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="F20" s="8" t="n">
         <v>983</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="G20" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="H20" s="8" t="n">
         <v>21087</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I20" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8629,24 +8890,27 @@
         <v>123</v>
       </c>
       <c r="D21" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="F21" s="8" t="n">
         <v>903</v>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="G21" s="8" t="n">
         <v>9.5</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="H21" s="8" t="n">
         <v>22775</v>
       </c>
-      <c r="H21" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8665,24 +8929,27 @@
         <v>200</v>
       </c>
       <c r="D22" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="F22" s="8" t="n">
         <v>917</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="G22" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="H22" s="8" t="n">
         <v>22128</v>
       </c>
-      <c r="H22" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I22" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8701,24 +8968,27 @@
         <v>170</v>
       </c>
       <c r="D23" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E23" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="F23" s="8" t="n">
         <v>928</v>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="G23" s="8" t="n">
         <v>9.5</v>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="H23" s="8" t="n">
         <v>27626</v>
       </c>
-      <c r="H23" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I23" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8737,24 +9007,27 @@
         <v>122</v>
       </c>
       <c r="D24" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="F24" s="8" t="n">
         <v>919</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="G24" s="8" t="n">
         <v>9.9</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="H24" s="8" t="n">
         <v>15532</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I24" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8773,24 +9046,27 @@
         <v>203</v>
       </c>
       <c r="D25" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="F25" s="8" t="n">
         <v>968</v>
       </c>
-      <c r="F25" s="8" t="n">
+      <c r="G25" s="8" t="n">
         <v>8.9</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="H25" s="8" t="n">
         <v>20181</v>
       </c>
-      <c r="H25" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8809,24 +9085,27 @@
         <v>422</v>
       </c>
       <c r="D26" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E26" s="8" t="n">
         <v>145</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="F26" s="8" t="n">
         <v>998</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="G26" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G26" s="8" t="n">
+      <c r="H26" s="8" t="n">
         <v>20122</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8845,24 +9124,27 @@
         <v>1070</v>
       </c>
       <c r="D27" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E27" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="E27" s="8" t="n">
+      <c r="F27" s="8" t="n">
         <v>1091</v>
       </c>
-      <c r="F27" s="8" t="n">
+      <c r="G27" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="H27" s="8" t="n">
         <v>26520</v>
       </c>
-      <c r="H27" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I27" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J27" s="8" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8881,24 +9163,27 @@
         <v>753</v>
       </c>
       <c r="D28" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="E28" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="F28" s="8" t="n">
         <v>1060</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="G28" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="H28" s="8" t="n">
         <v>27979</v>
       </c>
-      <c r="H28" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8917,24 +9202,27 @@
         <v>8368</v>
       </c>
       <c r="D29" s="8" t="n">
+        <v>279</v>
+      </c>
+      <c r="E29" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="F29" s="8" t="n">
         <v>1139</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="G29" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="H29" s="8" t="n">
         <v>33616</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="I29" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="J29" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J29" s="8" t="n">
+      <c r="K29" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8953,24 +9241,27 @@
         <v>126</v>
       </c>
       <c r="D30" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="F30" s="8" t="n">
         <v>925</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="G30" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="G30" s="8" t="n">
+      <c r="H30" s="8" t="n">
         <v>19028</v>
       </c>
-      <c r="H30" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I30" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8989,24 +9280,27 @@
         <v>1435</v>
       </c>
       <c r="D31" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="F31" s="8" t="n">
         <v>1056</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="G31" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="G31" s="8" t="n">
+      <c r="H31" s="8" t="n">
         <v>38274</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="I31" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I31" s="8" t="n">
+      <c r="J31" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="K31" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9025,24 +9319,27 @@
         <v>381</v>
       </c>
       <c r="D32" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="E32" s="8" t="n">
         <v>146</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="F32" s="8" t="n">
         <v>1027</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="G32" s="8" t="n">
         <v>9.6</v>
       </c>
-      <c r="G32" s="8" t="n">
+      <c r="H32" s="8" t="n">
         <v>21058</v>
       </c>
-      <c r="H32" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I32" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9061,24 +9358,27 @@
         <v>114</v>
       </c>
       <c r="D33" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E33" s="8" t="n">
+      <c r="F33" s="8" t="n">
         <v>910</v>
       </c>
-      <c r="F33" s="8" t="n">
+      <c r="G33" s="8" t="n">
         <v>9.6</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="H33" s="8" t="n">
         <v>25795</v>
       </c>
-      <c r="H33" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9097,24 +9397,27 @@
         <v>83</v>
       </c>
       <c r="D34" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E34" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="F34" s="8" t="n">
         <v>853</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="G34" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="H34" s="8" t="n">
         <v>17022</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9133,24 +9436,27 @@
         <v>2128</v>
       </c>
       <c r="D35" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="E35" s="8" t="n">
         <v>145</v>
       </c>
-      <c r="E35" s="8" t="n">
+      <c r="F35" s="8" t="n">
         <v>1113</v>
       </c>
-      <c r="F35" s="8" t="n">
+      <c r="G35" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="H35" s="8" t="n">
         <v>29426</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="I35" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="I35" s="8" t="n">
+      <c r="J35" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J35" s="8" t="n">
+      <c r="K35" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9169,24 +9475,27 @@
         <v>5093</v>
       </c>
       <c r="D36" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>145</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="F36" s="8" t="n">
         <v>1119</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="G36" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="H36" s="8" t="n">
         <v>34818</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="I36" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I36" s="8" t="n">
+      <c r="J36" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J36" s="8" t="n">
+      <c r="K36" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9205,24 +9514,27 @@
         <v>1792</v>
       </c>
       <c r="D37" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E37" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E37" s="8" t="n">
+      <c r="F37" s="8" t="n">
         <v>1093</v>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="G37" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="H37" s="8" t="n">
         <v>31778</v>
       </c>
-      <c r="H37" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I37" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="8" t="n">
+      <c r="K37" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9241,24 +9553,27 @@
         <v>326</v>
       </c>
       <c r="D38" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="F38" s="8" t="n">
         <v>971</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="G38" s="8" t="n">
         <v>9.5</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="H38" s="8" t="n">
         <v>22772</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I38" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9277,24 +9592,27 @@
         <v>72</v>
       </c>
       <c r="D39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="8" t="n">
         <v>145</v>
       </c>
-      <c r="E39" s="8" t="n">
+      <c r="F39" s="8" t="n">
         <v>864</v>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="G39" s="8" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="H39" s="8" t="n">
         <v>19585</v>
       </c>
-      <c r="H39" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9313,24 +9631,27 @@
         <v>166</v>
       </c>
       <c r="D40" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E40" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="F40" s="8" t="n">
         <v>926</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="G40" s="8" t="n">
         <v>9.6</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="H40" s="8" t="n">
         <v>18909</v>
       </c>
-      <c r="H40" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9349,24 +9670,27 @@
         <v>2059</v>
       </c>
       <c r="D41" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="E41" s="8" t="n">
         <v>146</v>
       </c>
-      <c r="E41" s="8" t="n">
+      <c r="F41" s="8" t="n">
         <v>1109</v>
       </c>
-      <c r="F41" s="8" t="n">
+      <c r="G41" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="H41" s="8" t="n">
         <v>35146</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="I41" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J41" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9385,24 +9709,27 @@
         <v>2419</v>
       </c>
       <c r="D42" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="E42" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="F42" s="8" t="n">
         <v>1090</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="G42" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="H42" s="8" t="n">
         <v>26990</v>
       </c>
-      <c r="H42" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J42" s="8" t="n">
+      <c r="K42" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9421,24 +9748,27 @@
         <v>1184</v>
       </c>
       <c r="D43" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="E43" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="E43" s="8" t="n">
+      <c r="F43" s="8" t="n">
         <v>1077</v>
       </c>
-      <c r="F43" s="8" t="n">
+      <c r="G43" s="8" t="n">
         <v>7.9</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="H43" s="8" t="n">
         <v>43758</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="I43" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I43" s="8" t="n">
+      <c r="J43" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J43" s="8" t="n">
+      <c r="K43" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9457,24 +9787,27 @@
         <v>9284</v>
       </c>
       <c r="D44" s="8" t="n">
+        <v>264</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>146</v>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="F44" s="8" t="n">
         <v>1128</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="G44" s="8" t="n">
         <v>7.7</v>
       </c>
-      <c r="G44" s="8" t="n">
+      <c r="H44" s="8" t="n">
         <v>29598</v>
       </c>
-      <c r="H44" s="8" t="n">
+      <c r="I44" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="I44" s="8" t="n">
+      <c r="J44" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="8" t="n">
+      <c r="K44" s="8" t="n">
         <v>50</v>
       </c>
     </row>
@@ -9493,24 +9826,27 @@
         <v>988</v>
       </c>
       <c r="D45" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="E45" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E45" s="8" t="n">
+      <c r="F45" s="8" t="n">
         <v>1047</v>
       </c>
-      <c r="F45" s="8" t="n">
+      <c r="G45" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="G45" s="8" t="n">
+      <c r="H45" s="8" t="n">
         <v>47382</v>
       </c>
-      <c r="H45" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I45" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J45" s="8" t="n">
+      <c r="K45" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9529,24 +9865,27 @@
         <v>616</v>
       </c>
       <c r="D46" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="E46" s="8" t="n">
         <v>146</v>
       </c>
-      <c r="E46" s="8" t="n">
+      <c r="F46" s="8" t="n">
         <v>1041</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="G46" s="8" t="n">
         <v>8.5</v>
       </c>
-      <c r="G46" s="8" t="n">
+      <c r="H46" s="8" t="n">
         <v>37787</v>
       </c>
-      <c r="H46" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9565,24 +9904,27 @@
         <v>1238</v>
       </c>
       <c r="D47" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="E47" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E47" s="8" t="n">
+      <c r="F47" s="8" t="n">
         <v>1106</v>
       </c>
-      <c r="F47" s="8" t="n">
+      <c r="G47" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="G47" s="8" t="n">
+      <c r="H47" s="8" t="n">
         <v>34357</v>
-      </c>
-      <c r="H47" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="I47" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J47" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9601,24 +9943,27 @@
         <v>406</v>
       </c>
       <c r="D48" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="E48" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E48" s="8" t="n">
+      <c r="F48" s="8" t="n">
         <v>1021</v>
       </c>
-      <c r="F48" s="8" t="n">
+      <c r="G48" s="8" t="n">
         <v>8.9</v>
       </c>
-      <c r="G48" s="8" t="n">
+      <c r="H48" s="8" t="n">
         <v>23133</v>
       </c>
-      <c r="H48" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9637,24 +9982,27 @@
         <v>8727</v>
       </c>
       <c r="D49" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="E49" s="8" t="n">
         <v>147</v>
       </c>
-      <c r="E49" s="8" t="n">
+      <c r="F49" s="8" t="n">
         <v>1138</v>
       </c>
-      <c r="F49" s="8" t="n">
+      <c r="G49" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G49" s="8" t="n">
+      <c r="H49" s="8" t="n">
         <v>31409</v>
       </c>
-      <c r="H49" s="8" t="n">
+      <c r="I49" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="I49" s="8" t="n">
+      <c r="J49" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J49" s="8" t="n">
+      <c r="K49" s="8" t="n">
         <v>14</v>
       </c>
     </row>
@@ -9673,24 +10021,27 @@
         <v>1787</v>
       </c>
       <c r="D50" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="E50" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="E50" s="8" t="n">
+      <c r="F50" s="8" t="n">
         <v>1102</v>
       </c>
-      <c r="F50" s="8" t="n">
+      <c r="G50" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="G50" s="8" t="n">
+      <c r="H50" s="8" t="n">
         <v>24146</v>
       </c>
-      <c r="H50" s="8" t="n">
+      <c r="I50" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I50" s="8" t="n">
+      <c r="J50" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J50" s="8" t="n">
+      <c r="K50" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9709,24 +10060,27 @@
         <v>6717</v>
       </c>
       <c r="D51" s="8" t="n">
+        <v>177</v>
+      </c>
+      <c r="E51" s="8" t="n">
         <v>150</v>
       </c>
-      <c r="E51" s="8" t="n">
+      <c r="F51" s="8" t="n">
         <v>1127</v>
       </c>
-      <c r="F51" s="8" t="n">
+      <c r="G51" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G51" s="8" t="n">
+      <c r="H51" s="8" t="n">
         <v>40957</v>
       </c>
-      <c r="H51" s="8" t="n">
+      <c r="I51" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="I51" s="8" t="n">
+      <c r="J51" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="8" t="n">
+      <c r="K51" s="8" t="n">
         <v>9</v>
       </c>
     </row>
@@ -9745,24 +10099,27 @@
         <v>2752</v>
       </c>
       <c r="D52" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="E52" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="E52" s="8" t="n">
+      <c r="F52" s="8" t="n">
         <v>1107</v>
       </c>
-      <c r="F52" s="8" t="n">
+      <c r="G52" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="G52" s="8" t="n">
+      <c r="H52" s="8" t="n">
         <v>29498</v>
       </c>
-      <c r="H52" s="8" t="n">
+      <c r="I52" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I52" s="8" t="n">
+      <c r="J52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J52" s="8" t="n">
+      <c r="K52" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9781,24 +10138,27 @@
         <v>4891</v>
       </c>
       <c r="D53" s="8" t="n">
+        <v>270</v>
+      </c>
+      <c r="E53" s="8" t="n">
         <v>149</v>
       </c>
-      <c r="E53" s="8" t="n">
+      <c r="F53" s="8" t="n">
         <v>1122</v>
       </c>
-      <c r="F53" s="8" t="n">
+      <c r="G53" s="8" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="G53" s="8" t="n">
+      <c r="H53" s="8" t="n">
         <v>36754</v>
       </c>
-      <c r="H53" s="8" t="n">
+      <c r="I53" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="I53" s="8" t="n">
+      <c r="J53" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J53" s="8" t="n">
+      <c r="K53" s="8" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9817,24 +10177,27 @@
         <v>5182</v>
       </c>
       <c r="D54" s="8" t="n">
+        <v>216</v>
+      </c>
+      <c r="E54" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="E54" s="8" t="n">
+      <c r="F54" s="8" t="n">
         <v>1127</v>
       </c>
-      <c r="F54" s="8" t="n">
+      <c r="G54" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="G54" s="8" t="n">
+      <c r="H54" s="8" t="n">
         <v>25820</v>
       </c>
-      <c r="H54" s="8" t="n">
+      <c r="I54" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I54" s="8" t="n">
+      <c r="J54" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="8" t="n">
+      <c r="K54" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9853,24 +10216,27 @@
         <v>543</v>
       </c>
       <c r="D55" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E55" s="8" t="n">
         <v>148</v>
       </c>
-      <c r="E55" s="8" t="n">
+      <c r="F55" s="8" t="n">
         <v>1061</v>
       </c>
-      <c r="F55" s="8" t="n">
+      <c r="G55" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="G55" s="8" t="n">
+      <c r="H55" s="8" t="n">
         <v>22257</v>
       </c>
-      <c r="H55" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I55" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9889,24 +10255,27 @@
         <v>1562</v>
       </c>
       <c r="D56" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="E56" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E56" s="8" t="n">
+      <c r="F56" s="8" t="n">
         <v>1079</v>
       </c>
-      <c r="F56" s="8" t="n">
+      <c r="G56" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G56" s="8" t="n">
+      <c r="H56" s="8" t="n">
         <v>43433</v>
       </c>
-      <c r="H56" s="8" t="n">
+      <c r="I56" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I56" s="8" t="n">
+      <c r="J56" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J56" s="8" t="n">
+      <c r="K56" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9925,24 +10294,27 @@
         <v>1706</v>
       </c>
       <c r="D57" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="E57" s="8" t="n">
         <v>143</v>
       </c>
-      <c r="E57" s="8" t="n">
+      <c r="F57" s="8" t="n">
         <v>1106</v>
       </c>
-      <c r="F57" s="8" t="n">
+      <c r="G57" s="8" t="n">
         <v>8.4</v>
       </c>
-      <c r="G57" s="8" t="n">
+      <c r="H57" s="8" t="n">
         <v>28426</v>
       </c>
-      <c r="H57" s="8" t="n">
+      <c r="I57" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="I57" s="8" t="n">
+      <c r="J57" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J57" s="8" t="n">
+      <c r="K57" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9961,24 +10333,27 @@
         <v>1015</v>
       </c>
       <c r="D58" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="E58" s="8" t="n">
         <v>144</v>
       </c>
-      <c r="E58" s="8" t="n">
+      <c r="F58" s="8" t="n">
         <v>1105</v>
       </c>
-      <c r="F58" s="8" t="n">
+      <c r="G58" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G58" s="8" t="n">
+      <c r="H58" s="8" t="n">
         <v>32322</v>
-      </c>
-      <c r="H58" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="I58" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J58" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K58" s="8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9997,24 +10372,27 @@
         <v>2489</v>
       </c>
       <c r="D59" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="E59" s="8" t="n">
         <v>145</v>
       </c>
-      <c r="E59" s="8" t="n">
+      <c r="F59" s="8" t="n">
         <v>1117</v>
       </c>
-      <c r="F59" s="8" t="n">
+      <c r="G59" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G59" s="8" t="n">
+      <c r="H59" s="8" t="n">
         <v>44402</v>
-      </c>
-      <c r="H59" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="I59" s="8" t="n">
         <v>3</v>
       </c>
       <c r="J59" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K59" s="8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10033,24 +10411,27 @@
         <v>2790</v>
       </c>
       <c r="D60" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="E60" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E60" s="8" t="n">
+      <c r="F60" s="8" t="n">
         <v>1116</v>
       </c>
-      <c r="F60" s="8" t="n">
+      <c r="G60" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="G60" s="8" t="n">
+      <c r="H60" s="8" t="n">
         <v>36016</v>
       </c>
-      <c r="H60" s="8" t="n">
+      <c r="I60" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="I60" s="8" t="n">
+      <c r="J60" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J60" s="8" t="n">
+      <c r="K60" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10069,24 +10450,27 @@
         <v>550</v>
       </c>
       <c r="D61" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E61" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="E61" s="8" t="n">
+      <c r="F61" s="8" t="n">
         <v>1029</v>
       </c>
-      <c r="F61" s="8" t="n">
+      <c r="G61" s="8" t="n">
         <v>7.9</v>
       </c>
-      <c r="G61" s="8" t="n">
+      <c r="H61" s="8" t="n">
         <v>35879</v>
       </c>
-      <c r="H61" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I61" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J61" s="8" t="n">
+      <c r="K61" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10105,24 +10489,27 @@
         <v>303</v>
       </c>
       <c r="D62" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E62" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="E62" s="8" t="n">
+      <c r="F62" s="8" t="n">
         <v>1003</v>
       </c>
-      <c r="F62" s="8" t="n">
+      <c r="G62" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="G62" s="8" t="n">
+      <c r="H62" s="8" t="n">
         <v>23389</v>
       </c>
-      <c r="H62" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I62" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10141,24 +10528,27 @@
         <v>210</v>
       </c>
       <c r="D63" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E63" s="8" t="n">
         <v>147</v>
       </c>
-      <c r="E63" s="8" t="n">
+      <c r="F63" s="8" t="n">
         <v>949</v>
       </c>
-      <c r="F63" s="8" t="n">
+      <c r="G63" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="G63" s="8" t="n">
+      <c r="H63" s="8" t="n">
         <v>19492</v>
       </c>
-      <c r="H63" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I63" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10177,24 +10567,27 @@
         <v>101</v>
       </c>
       <c r="D64" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E64" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E64" s="8" t="n">
+      <c r="F64" s="8" t="n">
         <v>893</v>
       </c>
-      <c r="F64" s="8" t="n">
+      <c r="G64" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="G64" s="8" t="n">
+      <c r="H64" s="8" t="n">
         <v>20663</v>
       </c>
-      <c r="H64" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I64" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10213,24 +10606,27 @@
         <v>3073</v>
       </c>
       <c r="D65" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="E65" s="8" t="n">
         <v>145</v>
       </c>
-      <c r="E65" s="8" t="n">
+      <c r="F65" s="8" t="n">
         <v>1119</v>
       </c>
-      <c r="F65" s="8" t="n">
+      <c r="G65" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="G65" s="8" t="n">
+      <c r="H65" s="8" t="n">
         <v>29859</v>
       </c>
-      <c r="H65" s="8" t="n">
+      <c r="I65" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="I65" s="8" t="n">
+      <c r="J65" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J65" s="8" t="n">
+      <c r="K65" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10249,24 +10645,27 @@
         <v>188</v>
       </c>
       <c r="D66" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" s="8" t="n">
         <v>140</v>
       </c>
-      <c r="E66" s="8" t="n">
+      <c r="F66" s="8" t="n">
         <v>991</v>
       </c>
-      <c r="F66" s="8" t="n">
+      <c r="G66" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="G66" s="8" t="n">
+      <c r="H66" s="8" t="n">
         <v>28320</v>
       </c>
-      <c r="H66" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I66" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10285,24 +10684,27 @@
         <v>788</v>
       </c>
       <c r="D67" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E67" s="8" t="n">
         <v>141</v>
       </c>
-      <c r="E67" s="8" t="n">
+      <c r="F67" s="8" t="n">
         <v>1027</v>
       </c>
-      <c r="F67" s="8" t="n">
+      <c r="G67" s="8" t="n">
         <v>8.5</v>
       </c>
-      <c r="G67" s="8" t="n">
+      <c r="H67" s="8" t="n">
         <v>35996</v>
       </c>
-      <c r="H67" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="I67" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J67" s="8" t="n">
+      <c r="K67" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10321,29 +10723,32 @@
         <v>426</v>
       </c>
       <c r="D68" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="E68" s="8" t="n">
         <v>142</v>
       </c>
-      <c r="E68" s="8" t="n">
+      <c r="F68" s="8" t="n">
         <v>970</v>
       </c>
-      <c r="F68" s="8" t="n">
+      <c r="G68" s="8" t="n">
         <v>9.5</v>
       </c>
-      <c r="G68" s="8" t="n">
+      <c r="H68" s="8" t="n">
         <v>19375</v>
       </c>
-      <c r="H68" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="I68" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="K68" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J68"/>
+  <autoFilter ref="A1:K68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11479,7 +11884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11549,89 +11954,101 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Sampling deficit</t>
+          <t>Environmental-pressure proxy</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Uniform: every Florida county has zero contaminant samples of any medium, so the deficit term does not discriminate within the study area.</t>
+          <t>fiokg EPA-PFAS-Facility records per county (4,118 in Florida; 188,057 nationally) — the PFAS-relevant subset of the EPA Facility Registry Service. All-FRS counts (118,663 in Florida of 4,955,792 nationally) are reported as a column but do NOT enter the score: FRS registers every site ever regulated or reported by EPA or a state programme, so it indexes economic activity more than PFAS risk. Verified 2026-07-29: log10 of the two measures correlates r = 0.943 across the 64 study counties, the top 8 counties are identical under either proxy, and the median absolute rank shift is 1 (max 12).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Infectious-disease filter</t>
+          <t>Sampling deficit</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>nde MONDO health conditions restricted by ubergraph rdfs:subClassOf* under MONDO:0005550 (infectious disease).</t>
+          <t>Uniform: every Florida county has zero contaminant samples of any medium, so the deficit term does not discriminate within the study area.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Human evidence</t>
+          <t>Infectious-disease filter</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>biohealth via ubergraph MONDO oboInOwl:hasDbXref -&gt; UMLS CUI node; oard-kg reified associations UNIONing biolink:subject and biolink:object; biomarkerkg OBCI_1000008/OBCI_1000002; prokn skos:exactMatch; spoke-okn DOID node IRIs via ubergraph skos:exactMatch.</t>
+          <t>nde MONDO health conditions restricted by ubergraph rdfs:subClassOf* under MONDO:0005550 (infectious disease).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Declared skips</t>
+          <t>Human evidence</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>GO and Reactome enrichment and drug/target linkage were not run: the study has no gene or protein foreground. biobricks-aopwiki (taxonomic applicability of adverse outcome pathways), rdkg, digcfdekg, gene-expression-atlas-okn, spoke-genelab, biobricks-mesh and spoke-okn organisms were considered and dropped with reasons in report section 6.4.</t>
+          <t>biohealth via ubergraph MONDO oboInOwl:hasDbXref -&gt; UMLS CUI node; oard-kg reified associations UNIONing biolink:subject and biolink:object; biomarkerkg OBCI_1000008/OBCI_1000002; prokn skos:exactMatch; spoke-okn DOID node IRIs via ubergraph skos:exactMatch.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Known defects surfaced</t>
+          <t>Declared skips</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Crosswalk L8 published verified_count is 63; the true Florida county count is 62 (one distinct value is the literal string 'https'). wildlifekn x sawgraph clade-expanded taxon overlap of 339 is an artefact of materialised phylum-level ancestors and must not be read as 339 species with contaminant data. biohealth asserts Anura-&gt;influenza (text-mining artefact) and misspells Colinus virginianus as 'Colinus virginiuanus' (silent false negative in the label bridge).</t>
+          <t>GO and Reactome enrichment and drug/target linkage were not run: the study has no gene or protein foreground. biobricks-aopwiki (taxonomic applicability of adverse outcome pathways), rdkg, digcfdekg, gene-expression-atlas-okn, spoke-genelab, biobricks-mesh and spoke-okn organisms were considered and dropped with reasons in report section 6.4.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Caveat carried to every claim</t>
+          <t>Known defects surfaced</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Hypothesis generation for sampling design; not exposure assessment, not causal or clinical inference. Observation counts index observer effort. Host-pathogen links are observational co-occurrence.</t>
+          <t>Crosswalk L8 published verified_count is 63; the true Florida county count is 62 (one distinct value is the literal string 'https'). wildlifekn x sawgraph clade-expanded taxon overlap of 339 is an artefact of materialised phylum-level ancestors and must not be read as 339 species with contaminant data. biohealth asserts Anura-&gt;influenza (text-mining artefact) and misspells Colinus virginianus as 'Colinus virginiuanus' (silent false negative in the label bridge).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
+          <t>Caveat carried to every claim</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Hypothesis generation for sampling design; not exposure assessment, not causal or clinical inference. Observation counts index observer effort. Host-pathogen links are observational co-occurrence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
           <t>Abbreviations</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>AI avian influenza; Bd Batrachochytrium dendrobatidis; CUI UMLS Concept Unique Identifier; DOID Human Disease Ontology; EEE eastern equine encephalitis; EHR electronic health record; FIPS Federal Information Processing Standards; FRS EPA Facility Registry Service; HP Human Phenotype Ontology; HPAI highly pathogenic avian influenza; IAV influenza A virus; KG knowledge graph; MONDO Mondo Disease Ontology; NCBITaxon NCBI Taxonomy; OKN Open Knowledge Network; PFAS per- and polyfluoroalkyl substances; PFOS perfluorooctanesulfonic acid; RCM regional climate model; S2 Google S2 cell hierarchy; SDoH social determinants of health; UMLS Unified Medical Language System; WNV West Nile virus; WQP US Water Quality Portal.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/examples/Sentinel-Wildlife/Sentinel-Wildlife_results.xlsx
+++ b/docs/examples/Sentinel-Wildlife/Sentinel-Wildlife_results.xlsx
@@ -24,7 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methods &amp; Rules" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ranked Results'!$A$1:$Z$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ranked Results'!$A$1:$Y$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Species Ranking'!$A$1:$T$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Observation Inventory'!$A$1:$G$401</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Observations by County'!$A$1:$G$197</definedName>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z65"/>
+  <dimension ref="A1:Y65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -514,12 +514,11 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="46" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="46" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -595,60 +594,55 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>EPA FRS facilities (all)</t>
+          <t>spoke-okn chemicals in county</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>spoke-okn chemicals in county</t>
+          <t>adult asthma %</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>adult asthma %</t>
+          <t>per-capita income USD</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>per-capita income USD</t>
+          <t>climatemodelskg places</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>climatemodelskg places</t>
+          <t>climate papers</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>climate papers</t>
+          <t>contaminant samples in county</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>contaminant samples in county</t>
+          <t>county bridge</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>county bridge</t>
+          <t>anchor lat</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>anchor lat</t>
+          <t>anchor lon</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>anchor lon</t>
+          <t>supporting KGs</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>supporting KGs</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>evidence</t>
         </is>
@@ -706,41 +700,38 @@
         <v>210</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>8727</v>
+        <v>147</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>147</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>31409</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>31409</v>
+        <v>12</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V2" s="2" t="n">
+        <v>28.49932056076961</v>
+      </c>
       <c r="W2" s="2" t="n">
-        <v>28.49932056076961</v>
+        <v>-81.57973854557652</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>-81.57973854557652</v>
-      </c>
-      <c r="Y2" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="Y2" s="3" t="inlineStr">
         <is>
           <t>11 sentinel-capable sp. (best tier M); 4 pathogen-host sp.; 110 spp. observed (86 bird / 24 amphibian); 210 EPA PFAS facilities of 8,727 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
@@ -798,41 +789,38 @@
         <v>264</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>9284</v>
+        <v>146</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>146</v>
+        <v>7.7</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>7.7</v>
+        <v>29598</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>29598</v>
+        <v>51</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V3" s="2" t="n">
+        <v>25.58527936881842</v>
+      </c>
       <c r="W3" s="2" t="n">
-        <v>25.58527936881842</v>
+        <v>-80.70451265047141</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>-80.70451265047141</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z3" s="2" t="inlineStr">
+      <c r="Y3" s="3" t="inlineStr">
         <is>
           <t>4 sentinel-capable sp. (best tier I1); 4 pathogen-host sp.; 107 spp. observed (88 bird / 19 amphibian); 264 EPA PFAS facilities of 9,284 FRS records; adult asthma 7.7%; contaminant samples in county: 0</t>
         </is>
@@ -890,41 +878,38 @@
         <v>177</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>6717</v>
+        <v>150</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>8</v>
+        <v>40957</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>40957</v>
+        <v>17</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V4" s="2" t="n">
+        <v>26.69963254942522</v>
+      </c>
       <c r="W4" s="2" t="n">
-        <v>26.69963254942522</v>
+        <v>-79.99199953131671</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>-79.99199953131671</v>
-      </c>
-      <c r="Y4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>5 sentinel-capable sp. (best tier I2); 4 pathogen-host sp.; 81 spp. observed (62 bird / 19 amphibian); 177 EPA PFAS facilities of 6,717 FRS records; adult asthma 8.0%; contaminant samples in county: 0</t>
         </is>
@@ -982,41 +967,38 @@
         <v>175</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>3929</v>
+        <v>149</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>149</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>33662</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>33662</v>
+        <v>7</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V5" s="2" t="n">
+        <v>28.24594282536288</v>
+      </c>
       <c r="W5" s="2" t="n">
-        <v>28.24594282536288</v>
+        <v>-80.83038906677767</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>-80.83038906677767</v>
-      </c>
-      <c r="Y5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z5" s="2" t="inlineStr">
+      <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>6 sentinel-capable sp. (best tier I1); 0 pathogen-host sp.; 84 spp. observed (71 bird / 13 amphibian); 175 EPA PFAS facilities of 3,929 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
@@ -1074,41 +1056,38 @@
         <v>66</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1505</v>
+        <v>144</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>144</v>
+        <v>9.1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>9.1</v>
+        <v>29821</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>29821</v>
+        <v>1</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="U6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V6" s="2" t="n">
+        <v>29.74767936437791</v>
+      </c>
       <c r="W6" s="2" t="n">
-        <v>29.74767936437791</v>
+        <v>-82.4299425913659</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>-82.4299425913659</v>
-      </c>
-      <c r="Y6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z6" s="2" t="inlineStr">
+      <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>5 sentinel-capable sp. (best tier I1); 0 pathogen-host sp.; 99 spp. observed (73 bird / 26 amphibian); 66 EPA PFAS facilities of 1,505 FRS records; adult asthma 9.1%; contaminant samples in county: 0</t>
         </is>
@@ -1166,41 +1145,38 @@
         <v>216</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>5182</v>
+        <v>144</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>144</v>
+        <v>9</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>9</v>
+        <v>25820</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>25820</v>
+        <v>6</v>
       </c>
       <c r="S7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>27.67591672557383</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>-81.48039780891368</v>
+      </c>
+      <c r="X7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="n">
-        <v>27.67591672557383</v>
-      </c>
-      <c r="X7" s="2" t="n">
-        <v>-81.48039780891368</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
+      <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>2 sentinel-capable sp. (best tier M); 1 pathogen-host sp.; 62 spp. observed (36 bird / 26 amphibian); 216 EPA PFAS facilities of 5,182 FRS records; adult asthma 9.0%; contaminant samples in county: 0</t>
         </is>
@@ -1258,16 +1234,16 @@
         <v>4</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>140</v>
+        <v>8.6</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>8.6</v>
+        <v>28320</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>28320</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>0</v>
@@ -1275,24 +1251,21 @@
       <c r="T8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V8" s="2" t="n">
+        <v>30.12320046555866</v>
+      </c>
       <c r="W8" s="2" t="n">
-        <v>30.12320046555866</v>
+        <v>-84.60080170880354</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>-84.60080170880354</v>
-      </c>
-      <c r="Y8" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="Z8" s="2" t="inlineStr">
+      <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>5 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 73 spp. observed (41 bird / 32 amphibian); 4 EPA PFAS facilities of 188 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
@@ -1350,41 +1323,38 @@
         <v>279</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>8368</v>
+        <v>144</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>144</v>
+        <v>8.1</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>8.1</v>
+        <v>33616</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>33616</v>
+        <v>23</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V9" s="2" t="n">
+        <v>28.01014547715257</v>
+      </c>
       <c r="W9" s="2" t="n">
-        <v>28.01014547715257</v>
+        <v>-82.418986425114</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>-82.418986425114</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
+      <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 62 spp. observed (38 bird / 24 amphibian); 279 EPA PFAS facilities of 8,368 FRS records; adult asthma 8.1%; contaminant samples in county: 0</t>
         </is>
@@ -1442,41 +1412,38 @@
         <v>270</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>4891</v>
+        <v>149</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>149</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>36754</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>36754</v>
+        <v>12</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V10" s="2" t="n">
+        <v>27.86565155117322</v>
+      </c>
       <c r="W10" s="2" t="n">
-        <v>27.86565155117322</v>
+        <v>-82.98420050849229</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>-82.98420050849229</v>
-      </c>
-      <c r="Y10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z10" s="2" t="inlineStr">
+      <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>3 sentinel-capable sp. (best tier I2); 1 pathogen-host sp.; 49 spp. observed (40 bird / 9 amphibian); 270 EPA PFAS facilities of 4,891 FRS records; adult asthma 8.7%; contaminant samples in county: 0</t>
         </is>
@@ -1534,41 +1501,38 @@
         <v>104</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>2489</v>
+        <v>145</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>8</v>
+        <v>44402</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>44402</v>
+        <v>3</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>27.32019707772083</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>-82.60251750242672</v>
+      </c>
+      <c r="X11" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="U11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="n">
-        <v>27.32019707772083</v>
-      </c>
-      <c r="X11" s="2" t="n">
-        <v>-82.60251750242672</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
+      <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>3 sentinel-capable sp. (best tier I2); 1 pathogen-host sp.; 63 spp. observed (53 bird / 10 amphibian); 104 EPA PFAS facilities of 2,489 FRS records; adult asthma 8.0%; contaminant samples in county: 0</t>
         </is>
@@ -1626,41 +1590,38 @@
         <v>31</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>1792</v>
+        <v>141</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>141</v>
+        <v>9.1</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>9.1</v>
+        <v>31778</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>31778</v>
+        <v>1</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V12" s="2" t="n">
+        <v>30.45472026465805</v>
+      </c>
       <c r="W12" s="2" t="n">
-        <v>30.45472026465805</v>
+        <v>-84.28561742869873</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>-84.28561742869873</v>
-      </c>
-      <c r="Y12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z12" s="2" t="inlineStr">
+      <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>3 sentinel-capable sp. (best tier M); 0 pathogen-host sp.; 39 spp. observed (16 bird / 23 amphibian); 31 EPA PFAS facilities of 1,792 FRS records; adult asthma 9.1%; contaminant samples in county: 0</t>
         </is>
@@ -1718,41 +1679,38 @@
         <v>79</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>2059</v>
+        <v>146</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>146</v>
+        <v>8.6</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>8.6</v>
+        <v>35146</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>35146</v>
+        <v>3</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V13" s="2" t="n">
+        <v>27.52895944163995</v>
+      </c>
       <c r="W13" s="2" t="n">
-        <v>27.52895944163995</v>
+        <v>-82.42958379039023</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>-82.42958379039023</v>
-      </c>
-      <c r="Y13" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>2 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 32 spp. observed (24 bird / 8 amphibian); 79 EPA PFAS facilities of 2,059 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
@@ -1810,41 +1768,38 @@
         <v>69</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1900</v>
+        <v>143</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>143</v>
+        <v>7.6</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>7.6</v>
+        <v>46785</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>46785</v>
+        <v>5</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V14" s="2" t="n">
+        <v>26.12475077294162</v>
+      </c>
       <c r="W14" s="2" t="n">
-        <v>26.12475077294162</v>
+        <v>-81.14631612119349</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>-81.14631612119349</v>
-      </c>
-      <c r="Y14" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z14" s="2" t="inlineStr">
+      <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>2 sentinel-capable sp. (best tier I4); 3 pathogen-host sp.; 70 spp. observed (52 bird / 18 amphibian); 69 EPA PFAS facilities of 1,900 FRS records; adult asthma 7.6%; contaminant samples in county: 0</t>
         </is>
@@ -1902,41 +1857,38 @@
         <v>70</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>2752</v>
+        <v>143</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>143</v>
+        <v>8.4</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>8.4</v>
+        <v>29498</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>29498</v>
+        <v>6</v>
       </c>
       <c r="S15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>verified L8</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>28.27818395167066</v>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>-82.7176991548576</v>
+      </c>
+      <c r="X15" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="T15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>verified L8</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="n">
-        <v>28.27818395167066</v>
-      </c>
-      <c r="X15" s="2" t="n">
-        <v>-82.7176991548576</v>
-      </c>
-      <c r="Y15" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z15" s="2" t="inlineStr">
+      <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>2 sentinel-capable sp. (best tier I2); 2 pathogen-host sp.; 31 spp. observed (15 bird / 16 amphibian); 70 EPA PFAS facilities of 2,752 FRS records; adult asthma 8.4%; contaminant samples in county: 0</t>
         </is>
@@ -1994,41 +1946,38 @@
         <v>118</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>5093</v>
+        <v>145</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>145</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>34818</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>34818</v>
+        <v>8</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V16" s="2" t="n">
+        <v>26.7466051081053</v>
+      </c>
       <c r="W16" s="2" t="n">
-        <v>26.7466051081053</v>
+        <v>-81.95127561002303</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>-81.95127561002303</v>
-      </c>
-      <c r="Y16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z16" s="2" t="inlineStr">
+      <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I1); 1 pathogen-host sp.; 47 spp. observed (34 bird / 13 amphibian); 118 EPA PFAS facilities of 5,093 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
@@ -2086,41 +2035,38 @@
         <v>26</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>1070</v>
+        <v>143</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>143</v>
+        <v>8.6</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>8.6</v>
+        <v>26520</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>26520</v>
+        <v>1</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="U17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V17" s="2" t="n">
+        <v>28.58129013344362</v>
+      </c>
       <c r="W17" s="2" t="n">
-        <v>28.58129013344362</v>
+        <v>-82.65724067139712</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>-82.65724067139712</v>
-      </c>
-      <c r="Y17" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier M); 1 pathogen-host sp.; 30 spp. observed (12 bird / 18 amphibian); 26 EPA PFAS facilities of 1,070 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
@@ -2178,41 +2124,38 @@
         <v>28</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>975</v>
+        <v>142</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>142</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>33275</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>33275</v>
+        <v>3</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
+      <c r="U18" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V18" s="4" t="n">
+        <v>26.95249181095944</v>
+      </c>
       <c r="W18" s="4" t="n">
-        <v>26.95249181095944</v>
+        <v>-82.00575596076499</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-82.00575596076499</v>
-      </c>
-      <c r="Y18" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z18" s="4" t="inlineStr">
+      <c r="Y18" s="5" t="inlineStr">
         <is>
           <t>2 sentinel-capable sp. (best tier I3); 2 pathogen-host sp.; 31 spp. observed (24 bird / 7 amphibian); 28 EPA PFAS facilities of 975 FRS records; adult asthma 8.8%; contaminant samples in county: 0</t>
         </is>
@@ -2270,41 +2213,38 @@
         <v>38</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1155</v>
+        <v>141</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>141</v>
+        <v>8.6</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>8.6</v>
+        <v>32037</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>32037</v>
+        <v>3</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
+      <c r="U19" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V19" s="4" t="n">
+        <v>30.06037823345315</v>
+      </c>
       <c r="W19" s="4" t="n">
-        <v>30.06037823345315</v>
+        <v>-81.82769081121819</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-81.82769081121819</v>
-      </c>
-      <c r="Y19" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z19" s="4" t="inlineStr">
+      <c r="Y19" s="5" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier M); 0 pathogen-host sp.; 24 spp. observed (8 bird / 16 amphibian); 38 EPA PFAS facilities of 1,155 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
@@ -2362,16 +2302,16 @@
         <v>28</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>619</v>
+        <v>142</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>142</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>28174</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>28174</v>
+        <v>0</v>
       </c>
       <c r="S20" s="4" t="n">
         <v>0</v>
@@ -2379,24 +2319,21 @@
       <c r="T20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
+      <c r="U20" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V20" s="4" t="n">
+        <v>28.82893634608188</v>
+      </c>
       <c r="W20" s="4" t="n">
-        <v>28.82893634608188</v>
+        <v>-82.66738038119389</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-82.66738038119389</v>
-      </c>
-      <c r="Y20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Z20" s="4" t="inlineStr">
+      <c r="Y20" s="5" t="inlineStr">
         <is>
           <t>3 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 39 spp. observed (26 bird / 13 amphibian); 28 EPA PFAS facilities of 619 FRS records; adult asthma 9.2%; contaminant samples in county: 0</t>
         </is>
@@ -2454,41 +2391,38 @@
         <v>56</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1015</v>
+        <v>144</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>144</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>32322</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>32322</v>
+        <v>3</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V21" s="4" t="n">
+        <v>30.9845463980149</v>
+      </c>
       <c r="W21" s="4" t="n">
-        <v>30.9845463980149</v>
+        <v>-86.96393265524841</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-86.96393265524841</v>
-      </c>
-      <c r="Y21" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z21" s="4" t="inlineStr">
+      <c r="Y21" s="5" t="inlineStr">
         <is>
           <t>2 sentinel-capable sp. (best tier I1); 0 pathogen-host sp.; 28 spp. observed (9 bird / 19 amphibian); 56 EPA PFAS facilities of 1,015 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
@@ -2546,16 +2480,16 @@
         <v>39</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>753</v>
+        <v>141</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>141</v>
+        <v>8.6</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>8.6</v>
+        <v>27979</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>27979</v>
+        <v>0</v>
       </c>
       <c r="S22" s="4" t="n">
         <v>0</v>
@@ -2563,24 +2497,21 @@
       <c r="T22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="4" t="inlineStr">
+      <c r="U22" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V22" s="4" t="n">
+        <v>27.33940919936872</v>
+      </c>
       <c r="W22" s="4" t="n">
-        <v>27.33940919936872</v>
+        <v>-81.3746008289168</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-81.3746008289168</v>
-      </c>
-      <c r="Y22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Z22" s="4" t="inlineStr">
+      <c r="Y22" s="5" t="inlineStr">
         <is>
           <t>2 sentinel-capable sp. (best tier I3); 1 pathogen-host sp.; 32 spp. observed (14 bird / 18 amphibian); 39 EPA PFAS facilities of 753 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
@@ -2638,41 +2569,38 @@
         <v>75</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2419</v>
+        <v>144</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>144</v>
+        <v>9</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>9</v>
+        <v>26990</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>26990</v>
+        <v>1</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="4" t="inlineStr">
+      <c r="U23" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V23" s="4" t="n">
+        <v>29.36382786445562</v>
+      </c>
       <c r="W23" s="4" t="n">
-        <v>29.36382786445562</v>
+        <v>-82.16948793283655</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-82.16948793283655</v>
-      </c>
-      <c r="Y23" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z23" s="4" t="inlineStr">
+      <c r="Y23" s="5" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 44 spp. observed (20 bird / 24 amphibian); 75 EPA PFAS facilities of 2,419 FRS records; adult asthma 9.0%; contaminant samples in county: 0</t>
         </is>
@@ -2730,41 +2658,38 @@
         <v>267</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7302</v>
+        <v>144</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>144</v>
+        <v>7.8</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>7.8</v>
+        <v>34063</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>34063</v>
+        <v>24</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="T24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="4" t="inlineStr">
+      <c r="U24" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V24" s="4" t="n">
+        <v>26.11823749256257</v>
+      </c>
       <c r="W24" s="4" t="n">
-        <v>26.11823749256257</v>
+        <v>-80.55238011597748</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-80.55238011597748</v>
-      </c>
-      <c r="Y24" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z24" s="4" t="inlineStr">
+      <c r="Y24" s="5" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 28 spp. observed (20 bird / 8 amphibian); 267 EPA PFAS facilities of 7,302 FRS records; adult asthma 7.8%; contaminant samples in county: 0</t>
         </is>
@@ -2822,41 +2747,38 @@
         <v>52</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1787</v>
+        <v>142</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>142</v>
+        <v>8.1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>8.1</v>
+        <v>24146</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>24146</v>
+        <v>4</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="4" t="inlineStr">
+      <c r="U25" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V25" s="4" t="n">
+        <v>28.25779299285393</v>
+      </c>
       <c r="W25" s="4" t="n">
-        <v>28.25779299285393</v>
+        <v>-81.30817852077075</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-81.30817852077075</v>
-      </c>
-      <c r="Y25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z25" s="4" t="inlineStr">
+      <c r="Y25" s="5" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I4); 2 pathogen-host sp.; 30 spp. observed (17 bird / 13 amphibian); 52 EPA PFAS facilities of 1,787 FRS records; adult asthma 8.1%; contaminant samples in county: 0</t>
         </is>
@@ -2914,41 +2836,38 @@
         <v>77</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2790</v>
+        <v>141</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>141</v>
+        <v>8</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>8</v>
+        <v>36016</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>36016</v>
+        <v>7</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="4" t="inlineStr">
+      <c r="U26" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V26" s="4" t="n">
+        <v>28.773993732448</v>
+      </c>
       <c r="W26" s="4" t="n">
-        <v>28.773993732448</v>
+        <v>-81.4040838957511</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-81.4040838957511</v>
-      </c>
-      <c r="Y26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z26" s="4" t="inlineStr">
+      <c r="Y26" s="5" t="inlineStr">
         <is>
           <t>2 sentinel-capable sp. (best tier I4); 1 pathogen-host sp.; 38 spp. observed (24 bird / 14 amphibian); 77 EPA PFAS facilities of 2,790 FRS records; adult asthma 8.0%; contaminant samples in county: 0</t>
         </is>
@@ -3006,41 +2925,38 @@
         <v>102</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>3073</v>
+        <v>145</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>145</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>29859</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>29859</v>
+        <v>8</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V27" s="4" t="n">
+        <v>28.7402627039306</v>
+      </c>
       <c r="W27" s="4" t="n">
-        <v>28.7402627039306</v>
+        <v>-80.77859334321759</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-80.77859334321759</v>
-      </c>
-      <c r="Y27" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z27" s="4" t="inlineStr">
+      <c r="Y27" s="5" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I2); 0 pathogen-host sp.; 26 spp. observed (15 bird / 11 amphibian); 102 EPA PFAS facilities of 3,073 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
@@ -3098,16 +3014,16 @@
         <v>24</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>422</v>
+        <v>145</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>145</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>20122</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>20122</v>
+        <v>0</v>
       </c>
       <c r="S28" s="4" t="n">
         <v>0</v>
@@ -3115,24 +3031,21 @@
       <c r="T28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
+      <c r="U28" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V28" s="4" t="n">
+        <v>26.58712411433794</v>
+      </c>
       <c r="W28" s="4" t="n">
-        <v>26.58712411433794</v>
+        <v>-81.11355434266586</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-81.11355434266586</v>
-      </c>
-      <c r="Y28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Z28" s="4" t="inlineStr">
+      <c r="Y28" s="5" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I4); 2 pathogen-host sp.; 23 spp. observed (8 bird / 15 amphibian); 24 EPA PFAS facilities of 422 FRS records; adult asthma 8.8%; contaminant samples in county: 0</t>
         </is>
@@ -3190,41 +3103,38 @@
         <v>72</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2342</v>
+        <v>151</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>151</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>29166</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>29166</v>
+        <v>9</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="4" t="inlineStr">
+      <c r="U29" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V29" s="4" t="n">
+        <v>30.77900285928655</v>
+      </c>
       <c r="W29" s="4" t="n">
-        <v>30.77900285928655</v>
+        <v>-87.37585586179792</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-87.37585586179792</v>
-      </c>
-      <c r="Y29" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z29" s="4" t="inlineStr">
+      <c r="Y29" s="5" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I3); 0 pathogen-host sp.; 42 spp. observed (15 bird / 27 amphibian); 72 EPA PFAS facilities of 2,342 FRS records; adult asthma 9.3%; contaminant samples in county: 0</t>
         </is>
@@ -3282,16 +3192,16 @@
         <v>27</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>406</v>
+        <v>141</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>141</v>
+        <v>8.9</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>8.9</v>
+        <v>23133</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>23133</v>
+        <v>0</v>
       </c>
       <c r="S30" s="4" t="n">
         <v>0</v>
@@ -3299,24 +3209,21 @@
       <c r="T30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="4" t="inlineStr">
+      <c r="U30" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V30" s="4" t="n">
+        <v>27.01700782445687</v>
+      </c>
       <c r="W30" s="4" t="n">
-        <v>27.01700782445687</v>
+        <v>-80.82670027712663</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-80.82670027712663</v>
-      </c>
-      <c r="Y30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Z30" s="4" t="inlineStr">
+      <c r="Y30" s="5" t="inlineStr">
         <is>
           <t>2 sentinel-capable sp. (best tier I3); 0 pathogen-host sp.; 26 spp. observed (14 bird / 12 amphibian); 27 EPA PFAS facilities of 406 FRS records; adult asthma 8.9%; contaminant samples in county: 0</t>
         </is>
@@ -3374,16 +3281,16 @@
         <v>8</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>140</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>19911</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>19911</v>
+        <v>0</v>
       </c>
       <c r="S31" s="4" t="n">
         <v>0</v>
@@ -3391,24 +3298,21 @@
       <c r="T31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="4" t="inlineStr">
+      <c r="U31" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V31" s="4" t="n">
+        <v>29.45565233248205</v>
+      </c>
       <c r="W31" s="4" t="n">
-        <v>29.45565233248205</v>
+        <v>-83.3660880353189</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-83.3660880353189</v>
-      </c>
-      <c r="Y31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Z31" s="4" t="inlineStr">
+      <c r="Y31" s="5" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I3); 1 pathogen-host sp.; 7 spp. observed (3 bird / 4 amphibian); 8 EPA PFAS facilities of 110 FRS records; adult asthma 9.8%; contaminant samples in county: 0</t>
         </is>
@@ -3466,41 +3370,38 @@
         <v>39</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1562</v>
+        <v>141</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>141</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>43433</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>43433</v>
+        <v>4</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
+      <c r="U32" s="4" t="inlineStr">
         <is>
           <t>repaired Saint-&gt;St.</t>
         </is>
       </c>
+      <c r="V32" s="4" t="n">
+        <v>29.84898480155067</v>
+      </c>
       <c r="W32" s="4" t="n">
-        <v>29.84898480155067</v>
+        <v>-81.21699840343739</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-81.21699840343739</v>
-      </c>
-      <c r="Y32" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z32" s="4" t="inlineStr">
+      <c r="Y32" s="5" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I4); 1 pathogen-host sp.; 26 spp. observed (12 bird / 14 amphibian); 39 EPA PFAS facilities of 1,562 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
@@ -3558,16 +3459,16 @@
         <v>28</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>543</v>
+        <v>148</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>148</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>22257</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>22257</v>
+        <v>0</v>
       </c>
       <c r="S33" s="4" t="n">
         <v>0</v>
@@ -3575,24 +3476,21 @@
       <c r="T33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="4" t="inlineStr">
+      <c r="U33" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V33" s="4" t="n">
+        <v>29.64367220657317</v>
+      </c>
       <c r="W33" s="4" t="n">
-        <v>29.64367220657317</v>
+        <v>-81.78027808142588</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-81.78027808142588</v>
-      </c>
-      <c r="Y33" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Z33" s="4" t="inlineStr">
+      <c r="Y33" s="5" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 26 spp. observed (9 bird / 17 amphibian); 28 EPA PFAS facilities of 543 FRS records; adult asthma 9.7%; contaminant samples in county: 0</t>
         </is>
@@ -3650,41 +3548,38 @@
         <v>58</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2128</v>
+        <v>145</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>145</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>8.300000000000001</v>
+        <v>29426</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>29426</v>
+        <v>5</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="4" t="inlineStr">
+      <c r="U34" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V34" s="4" t="n">
+        <v>28.62392183557449</v>
+      </c>
       <c r="W34" s="4" t="n">
-        <v>28.62392183557449</v>
+        <v>-81.79124705895957</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-81.79124705895957</v>
-      </c>
-      <c r="Y34" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z34" s="4" t="inlineStr">
+      <c r="Y34" s="5" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 29 spp. observed (14 bird / 15 amphibian); 58 EPA PFAS facilities of 2,128 FRS records; adult asthma 8.3%; contaminant samples in county: 0</t>
         </is>
@@ -3742,16 +3637,16 @@
         <v>23</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>381</v>
+        <v>146</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>146</v>
+        <v>9.6</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>9.6</v>
+        <v>21058</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>21058</v>
+        <v>0</v>
       </c>
       <c r="S35" s="4" t="n">
         <v>0</v>
@@ -3759,24 +3654,21 @@
       <c r="T35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="4" t="inlineStr">
+      <c r="U35" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V35" s="4" t="n">
+        <v>30.85166845762893</v>
+      </c>
       <c r="W35" s="4" t="n">
-        <v>30.85166845762893</v>
+        <v>-85.11492966299454</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-85.11492966299454</v>
-      </c>
-      <c r="Y35" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Z35" s="4" t="inlineStr">
+      <c r="Y35" s="5" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 26 spp. observed (1 bird / 25 amphibian); 23 EPA PFAS facilities of 381 FRS records; adult asthma 9.6%; contaminant samples in county: 0</t>
         </is>
@@ -3834,16 +3726,16 @@
         <v>6</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>140</v>
+        <v>8.9</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>8.9</v>
+        <v>26211</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>26211</v>
+        <v>0</v>
       </c>
       <c r="S36" s="4" t="n">
         <v>0</v>
@@ -3851,24 +3743,21 @@
       <c r="T36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="4" t="inlineStr">
+      <c r="U36" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V36" s="4" t="n">
+        <v>29.96571430542564</v>
+      </c>
       <c r="W36" s="4" t="n">
-        <v>29.96571430542564</v>
+        <v>-84.70126741314157</v>
       </c>
       <c r="X36" s="4" t="n">
-        <v>-84.70126741314157</v>
-      </c>
-      <c r="Y36" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Z36" s="4" t="inlineStr">
+      <c r="Y36" s="5" t="inlineStr">
         <is>
           <t>1 sentinel-capable sp. (best tier I4); 0 pathogen-host sp.; 35 spp. observed (13 bird / 22 amphibian); 6 EPA PFAS facilities of 142 FRS records; adult asthma 8.9%; contaminant samples in county: 0</t>
         </is>
@@ -3926,41 +3815,38 @@
         <v>41</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>1184</v>
+        <v>142</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>142</v>
+        <v>7.9</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>7.9</v>
+        <v>43758</v>
       </c>
       <c r="R37" s="4" t="n">
-        <v>43758</v>
+        <v>2</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="4" t="inlineStr">
+      <c r="U37" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V37" s="4" t="n">
+        <v>26.97300700137653</v>
+      </c>
       <c r="W37" s="4" t="n">
-        <v>26.97300700137653</v>
+        <v>-80.46357061141781</v>
       </c>
       <c r="X37" s="4" t="n">
-        <v>-80.46357061141781</v>
-      </c>
-      <c r="Y37" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z37" s="4" t="inlineStr">
+      <c r="Y37" s="5" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 28 spp. observed (15 bird / 13 amphibian); 41 EPA PFAS facilities of 1,184 FRS records; adult asthma 7.9%; contaminant samples in county: 0</t>
         </is>
@@ -4018,16 +3904,16 @@
         <v>7</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>140</v>
+        <v>9.6</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>9.6</v>
+        <v>25795</v>
       </c>
       <c r="R38" s="4" t="n">
-        <v>25795</v>
+        <v>0</v>
       </c>
       <c r="S38" s="4" t="n">
         <v>0</v>
@@ -4035,24 +3921,21 @@
       <c r="T38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="4" t="inlineStr">
+      <c r="U38" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V38" s="4" t="n">
+        <v>30.19800765490457</v>
+      </c>
       <c r="W38" s="4" t="n">
-        <v>30.19800765490457</v>
+        <v>-84.02905852163313</v>
       </c>
       <c r="X38" s="4" t="n">
-        <v>-84.02905852163313</v>
-      </c>
-      <c r="Y38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="Z38" s="4" t="inlineStr">
+      <c r="Y38" s="5" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 17 spp. observed (1 bird / 16 amphibian); 7 EPA PFAS facilities of 114 FRS records; adult asthma 9.6%; contaminant samples in county: 0</t>
         </is>
@@ -4110,41 +3993,38 @@
         <v>38</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>988</v>
+        <v>141</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>141</v>
+        <v>7.5</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>7.5</v>
+        <v>47382</v>
       </c>
       <c r="R39" s="4" t="n">
-        <v>47382</v>
+        <v>1</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="U39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="4" t="inlineStr">
+      <c r="U39" s="4" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V39" s="4" t="n">
+        <v>25.13947963570052</v>
+      </c>
       <c r="W39" s="4" t="n">
-        <v>25.13947963570052</v>
+        <v>-81.6540785876179</v>
       </c>
       <c r="X39" s="4" t="n">
-        <v>-81.6540785876179</v>
-      </c>
-      <c r="Y39" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="Z39" s="4" t="inlineStr">
+      <c r="Y39" s="5" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 58 spp. observed (45 bird / 13 amphibian); 38 EPA PFAS facilities of 988 FRS records; adult asthma 7.5%; contaminant samples in county: 0</t>
         </is>
@@ -4202,16 +4082,16 @@
         <v>27</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>402</v>
+        <v>146</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>146</v>
+        <v>10.4</v>
       </c>
       <c r="Q40" s="6" t="n">
-        <v>10.4</v>
+        <v>21087</v>
       </c>
       <c r="R40" s="6" t="n">
-        <v>21087</v>
+        <v>0</v>
       </c>
       <c r="S40" s="6" t="n">
         <v>0</v>
@@ -4219,24 +4099,21 @@
       <c r="T40" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="6" t="inlineStr">
+      <c r="U40" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V40" s="6" t="n">
+        <v>30.54571566514775</v>
+      </c>
       <c r="W40" s="6" t="n">
-        <v>30.54571566514775</v>
+        <v>-84.53430424051304</v>
       </c>
       <c r="X40" s="6" t="n">
-        <v>-84.53430424051304</v>
-      </c>
-      <c r="Y40" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z40" s="6" t="inlineStr">
+      <c r="Y40" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 19 spp. observed (4 bird / 15 amphibian); 27 EPA PFAS facilities of 402 FRS records; adult asthma 10.4%; contaminant samples in county: 0</t>
         </is>
@@ -4294,41 +4171,38 @@
         <v>56</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1238</v>
+        <v>141</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>141</v>
+        <v>8.6</v>
       </c>
       <c r="Q41" s="6" t="n">
-        <v>8.6</v>
+        <v>34357</v>
       </c>
       <c r="R41" s="6" t="n">
-        <v>34357</v>
+        <v>3</v>
       </c>
       <c r="S41" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T41" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="6" t="inlineStr">
+      <c r="U41" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V41" s="6" t="n">
+        <v>30.76545882256282</v>
+      </c>
       <c r="W41" s="6" t="n">
-        <v>30.76545882256282</v>
+        <v>-86.7600696602539</v>
       </c>
       <c r="X41" s="6" t="n">
-        <v>-86.7600696602539</v>
-      </c>
-      <c r="Y41" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Z41" s="6" t="inlineStr">
+      <c r="Y41" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 29 spp. observed (8 bird / 21 amphibian); 56 EPA PFAS facilities of 1,238 FRS records; adult asthma 8.6%; contaminant samples in county: 0</t>
         </is>
@@ -4386,41 +4260,38 @@
         <v>67</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1617</v>
+        <v>143</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>143</v>
+        <v>8.9</v>
       </c>
       <c r="Q42" s="6" t="n">
-        <v>8.9</v>
+        <v>30774</v>
       </c>
       <c r="R42" s="6" t="n">
-        <v>30774</v>
+        <v>2</v>
       </c>
       <c r="S42" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="6" t="inlineStr">
+      <c r="U42" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V42" s="6" t="n">
+        <v>30.06380432335288</v>
+      </c>
       <c r="W42" s="6" t="n">
-        <v>30.06380432335288</v>
+        <v>-85.59707056676258</v>
       </c>
       <c r="X42" s="6" t="n">
-        <v>-85.59707056676258</v>
-      </c>
-      <c r="Y42" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Z42" s="6" t="inlineStr">
+      <c r="Y42" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 15 spp. observed (4 bird / 11 amphibian); 67 EPA PFAS facilities of 1,617 FRS records; adult asthma 8.9%; contaminant samples in county: 0</t>
         </is>
@@ -4478,16 +4349,16 @@
         <v>25</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>326</v>
+        <v>141</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>141</v>
+        <v>9.5</v>
       </c>
       <c r="Q43" s="6" t="n">
-        <v>9.5</v>
+        <v>22772</v>
       </c>
       <c r="R43" s="6" t="n">
-        <v>22772</v>
+        <v>0</v>
       </c>
       <c r="S43" s="6" t="n">
         <v>0</v>
@@ -4495,24 +4366,21 @@
       <c r="T43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="6" t="inlineStr">
+      <c r="U43" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V43" s="6" t="n">
+        <v>29.1524113491336</v>
+      </c>
       <c r="W43" s="6" t="n">
-        <v>29.1524113491336</v>
+        <v>-82.94070012870873</v>
       </c>
       <c r="X43" s="6" t="n">
-        <v>-82.94070012870873</v>
-      </c>
-      <c r="Y43" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z43" s="6" t="inlineStr">
+      <c r="Y43" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 23 spp. observed (7 bird / 16 amphibian); 25 EPA PFAS facilities of 326 FRS records; adult asthma 9.5%; contaminant samples in county: 0</t>
         </is>
@@ -4570,16 +4438,16 @@
         <v>35</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>426</v>
+        <v>142</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>142</v>
+        <v>9.5</v>
       </c>
       <c r="Q44" s="6" t="n">
-        <v>9.5</v>
+        <v>19375</v>
       </c>
       <c r="R44" s="6" t="n">
-        <v>19375</v>
+        <v>0</v>
       </c>
       <c r="S44" s="6" t="n">
         <v>0</v>
@@ -4587,24 +4455,21 @@
       <c r="T44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="6" t="inlineStr">
+      <c r="U44" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V44" s="6" t="n">
+        <v>30.68708643605398</v>
+      </c>
       <c r="W44" s="6" t="n">
-        <v>30.68708643605398</v>
+        <v>-85.65498721979255</v>
       </c>
       <c r="X44" s="6" t="n">
-        <v>-85.65498721979255</v>
-      </c>
-      <c r="Y44" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z44" s="6" t="inlineStr">
+      <c r="Y44" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 13 spp. observed (1 bird / 12 amphibian); 35 EPA PFAS facilities of 426 FRS records; adult asthma 9.5%; contaminant samples in county: 0</t>
         </is>
@@ -4662,16 +4527,16 @@
         <v>1</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>145</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q45" s="6" t="n">
-        <v>9.300000000000001</v>
+        <v>19585</v>
       </c>
       <c r="R45" s="6" t="n">
-        <v>19585</v>
+        <v>0</v>
       </c>
       <c r="S45" s="6" t="n">
         <v>0</v>
@@ -4679,24 +4544,21 @@
       <c r="T45" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="6" t="inlineStr">
+      <c r="U45" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V45" s="6" t="n">
+        <v>30.38733255651748</v>
+      </c>
       <c r="W45" s="6" t="n">
-        <v>30.38733255651748</v>
+        <v>-84.87934954093932</v>
       </c>
       <c r="X45" s="6" t="n">
-        <v>-84.87934954093932</v>
-      </c>
-      <c r="Y45" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z45" s="6" t="inlineStr">
+      <c r="Y45" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 1 pathogen-host sp.; 29 spp. observed (2 bird / 27 amphibian); 1 EPA PFAS facilities of 72 FRS records; adult asthma 9.3%; contaminant samples in county: 0</t>
         </is>
@@ -4754,16 +4616,16 @@
         <v>17</v>
       </c>
       <c r="O46" s="6" t="n">
-        <v>434</v>
+        <v>143</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>143</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q46" s="6" t="n">
-        <v>9.699999999999999</v>
+        <v>24569</v>
       </c>
       <c r="R46" s="6" t="n">
-        <v>24569</v>
+        <v>0</v>
       </c>
       <c r="S46" s="6" t="n">
         <v>0</v>
@@ -4771,24 +4633,21 @@
       <c r="T46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="6" t="inlineStr">
+      <c r="U46" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V46" s="6" t="n">
+        <v>30.26974293797891</v>
+      </c>
       <c r="W46" s="6" t="n">
-        <v>30.26974293797891</v>
+        <v>-82.58522833564639</v>
       </c>
       <c r="X46" s="6" t="n">
-        <v>-82.58522833564639</v>
-      </c>
-      <c r="Y46" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z46" s="6" t="inlineStr">
+      <c r="Y46" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 12 spp. observed (3 bird / 9 amphibian); 17 EPA PFAS facilities of 434 FRS records; adult asthma 9.7%; contaminant samples in county: 0</t>
         </is>
@@ -4846,41 +4705,38 @@
         <v>52</v>
       </c>
       <c r="O47" s="6" t="n">
-        <v>1706</v>
+        <v>143</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>143</v>
+        <v>8.4</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>8.4</v>
+        <v>28426</v>
       </c>
       <c r="R47" s="6" t="n">
-        <v>28426</v>
+        <v>2</v>
       </c>
       <c r="S47" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="6" t="inlineStr">
+      <c r="U47" s="6" t="inlineStr">
         <is>
           <t>repaired Saint-&gt;St.</t>
         </is>
       </c>
+      <c r="V47" s="6" t="n">
+        <v>27.44682143438291</v>
+      </c>
       <c r="W47" s="6" t="n">
-        <v>27.44682143438291</v>
+        <v>-80.51948770224774</v>
       </c>
       <c r="X47" s="6" t="n">
-        <v>-80.51948770224774</v>
-      </c>
-      <c r="Y47" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Z47" s="6" t="inlineStr">
+      <c r="Y47" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 10 spp. observed (4 bird / 6 amphibian); 52 EPA PFAS facilities of 1,706 FRS records; adult asthma 8.4%; contaminant samples in county: 0</t>
         </is>
@@ -4938,41 +4794,38 @@
         <v>23</v>
       </c>
       <c r="O48" s="6" t="n">
-        <v>1435</v>
+        <v>143</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>143</v>
+        <v>8.4</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>8.4</v>
+        <v>38274</v>
       </c>
       <c r="R48" s="6" t="n">
-        <v>38274</v>
+        <v>4</v>
       </c>
       <c r="S48" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="U48" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V48" s="6" t="n">
+        <v>27.67141007273313</v>
+      </c>
       <c r="W48" s="6" t="n">
-        <v>27.67141007273313</v>
+        <v>-80.63046059303447</v>
       </c>
       <c r="X48" s="6" t="n">
-        <v>-80.63046059303447</v>
-      </c>
-      <c r="Y48" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Z48" s="6" t="inlineStr">
+      <c r="Y48" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 24 spp. observed (14 bird / 10 amphibian); 23 EPA PFAS facilities of 1,435 FRS records; adult asthma 8.4%; contaminant samples in county: 0</t>
         </is>
@@ -5030,16 +4883,16 @@
         <v>29</v>
       </c>
       <c r="O49" s="6" t="n">
-        <v>616</v>
+        <v>146</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>146</v>
+        <v>8.5</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>8.5</v>
+        <v>37787</v>
       </c>
       <c r="R49" s="6" t="n">
-        <v>37787</v>
+        <v>0</v>
       </c>
       <c r="S49" s="6" t="n">
         <v>0</v>
@@ -5047,24 +4900,21 @@
       <c r="T49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="6" t="inlineStr">
+      <c r="U49" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V49" s="6" t="n">
+        <v>30.49246958955147</v>
+      </c>
       <c r="W49" s="6" t="n">
-        <v>30.49246958955147</v>
+        <v>-81.53918408848806</v>
       </c>
       <c r="X49" s="6" t="n">
-        <v>-81.53918408848806</v>
-      </c>
-      <c r="Y49" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z49" s="6" t="inlineStr">
+      <c r="Y49" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 15 spp. observed (8 bird / 7 amphibian); 29 EPA PFAS facilities of 616 FRS records; adult asthma 8.5%; contaminant samples in county: 0</t>
         </is>
@@ -5122,16 +4972,16 @@
         <v>15</v>
       </c>
       <c r="O50" s="6" t="n">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>147</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q50" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>19492</v>
       </c>
       <c r="R50" s="6" t="n">
-        <v>19492</v>
+        <v>0</v>
       </c>
       <c r="S50" s="6" t="n">
         <v>0</v>
@@ -5139,24 +4989,21 @@
       <c r="T50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="6" t="inlineStr">
+      <c r="U50" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V50" s="6" t="n">
+        <v>29.86777249166445</v>
+      </c>
       <c r="W50" s="6" t="n">
-        <v>29.86777249166445</v>
+        <v>-83.38071940996305</v>
       </c>
       <c r="X50" s="6" t="n">
-        <v>-83.38071940996305</v>
-      </c>
-      <c r="Y50" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z50" s="6" t="inlineStr">
+      <c r="Y50" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 3 spp. observed (2 bird / 1 amphibian); 15 EPA PFAS facilities of 210 FRS records; adult asthma 9.8%; contaminant samples in county: 0</t>
         </is>
@@ -5214,41 +5061,38 @@
         <v>19</v>
       </c>
       <c r="O51" s="6" t="n">
-        <v>788</v>
+        <v>141</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>141</v>
+        <v>8.5</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>8.5</v>
+        <v>35996</v>
       </c>
       <c r="R51" s="6" t="n">
-        <v>35996</v>
+        <v>1</v>
       </c>
       <c r="S51" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="6" t="inlineStr">
+      <c r="U51" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V51" s="6" t="n">
+        <v>30.2401971508469</v>
+      </c>
       <c r="W51" s="6" t="n">
-        <v>30.2401971508469</v>
+        <v>-86.32236411121448</v>
       </c>
       <c r="X51" s="6" t="n">
-        <v>-86.32236411121448</v>
-      </c>
-      <c r="Y51" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Z51" s="6" t="inlineStr">
+      <c r="Y51" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 17 spp. observed (6 bird / 11 amphibian); 19 EPA PFAS facilities of 788 FRS records; adult asthma 8.5%; contaminant samples in county: 0</t>
         </is>
@@ -5306,16 +5150,16 @@
         <v>8</v>
       </c>
       <c r="O52" s="6" t="n">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>141</v>
+        <v>9.5</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>9.5</v>
+        <v>27626</v>
       </c>
       <c r="R52" s="6" t="n">
-        <v>27626</v>
+        <v>0</v>
       </c>
       <c r="S52" s="6" t="n">
         <v>0</v>
@@ -5323,24 +5167,21 @@
       <c r="T52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="6" t="inlineStr">
+      <c r="U52" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V52" s="6" t="n">
+        <v>29.80367220010124</v>
+      </c>
       <c r="W52" s="6" t="n">
-        <v>29.80367220010124</v>
+        <v>-85.19096920056063</v>
       </c>
       <c r="X52" s="6" t="n">
-        <v>-85.19096920056063</v>
-      </c>
-      <c r="Y52" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z52" s="6" t="inlineStr">
+      <c r="Y52" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 15 spp. observed (4 bird / 11 amphibian); 8 EPA PFAS facilities of 170 FRS records; adult asthma 9.5%; contaminant samples in county: 0</t>
         </is>
@@ -5398,16 +5239,16 @@
         <v>18</v>
       </c>
       <c r="O53" s="6" t="n">
-        <v>303</v>
+        <v>142</v>
       </c>
       <c r="P53" s="6" t="n">
-        <v>142</v>
+        <v>9.1</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>9.1</v>
+        <v>23389</v>
       </c>
       <c r="R53" s="6" t="n">
-        <v>23389</v>
+        <v>0</v>
       </c>
       <c r="S53" s="6" t="n">
         <v>0</v>
@@ -5415,24 +5256,21 @@
       <c r="T53" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="6" t="inlineStr">
+      <c r="U53" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V53" s="6" t="n">
+        <v>30.01770471466019</v>
+      </c>
       <c r="W53" s="6" t="n">
-        <v>30.01770471466019</v>
+        <v>-82.79762265632753</v>
       </c>
       <c r="X53" s="6" t="n">
-        <v>-82.79762265632753</v>
-      </c>
-      <c r="Y53" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z53" s="6" t="inlineStr">
+      <c r="Y53" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 5 spp. observed (1 bird / 4 amphibian); 18 EPA PFAS facilities of 303 FRS records; adult asthma 9.1%; contaminant samples in county: 0</t>
         </is>
@@ -5490,16 +5328,16 @@
         <v>14</v>
       </c>
       <c r="O54" s="6" t="n">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>143</v>
+        <v>9.6</v>
       </c>
       <c r="Q54" s="6" t="n">
-        <v>9.6</v>
+        <v>18909</v>
       </c>
       <c r="R54" s="6" t="n">
-        <v>18909</v>
+        <v>0</v>
       </c>
       <c r="S54" s="6" t="n">
         <v>0</v>
@@ -5507,24 +5345,21 @@
       <c r="T54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="6" t="inlineStr">
+      <c r="U54" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V54" s="6" t="n">
+        <v>30.43237542370881</v>
+      </c>
       <c r="W54" s="6" t="n">
-        <v>30.43237542370881</v>
+        <v>-83.48353451957558</v>
       </c>
       <c r="X54" s="6" t="n">
-        <v>-83.48353451957558</v>
-      </c>
-      <c r="Y54" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z54" s="6" t="inlineStr">
+      <c r="Y54" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 2 spp. observed (0 bird / 2 amphibian); 14 EPA PFAS facilities of 166 FRS records; adult asthma 9.6%; contaminant samples in county: 0</t>
         </is>
@@ -5582,16 +5417,16 @@
         <v>9</v>
       </c>
       <c r="O55" s="6" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>141</v>
+        <v>10.1</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>10.1</v>
+        <v>19028</v>
       </c>
       <c r="R55" s="6" t="n">
-        <v>19028</v>
+        <v>0</v>
       </c>
       <c r="S55" s="6" t="n">
         <v>0</v>
@@ -5599,24 +5434,21 @@
       <c r="T55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="6" t="inlineStr">
+      <c r="U55" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V55" s="6" t="n">
+        <v>30.8589109524587</v>
+      </c>
       <c r="W55" s="6" t="n">
-        <v>30.8589109524587</v>
+        <v>-85.8772468924296</v>
       </c>
       <c r="X55" s="6" t="n">
-        <v>-85.8772468924296</v>
-      </c>
-      <c r="Y55" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z55" s="6" t="inlineStr">
+      <c r="Y55" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 1 spp. observed (0 bird / 1 amphibian); 9 EPA PFAS facilities of 126 FRS records; adult asthma 10.1%; contaminant samples in county: 0</t>
         </is>
@@ -5674,41 +5506,38 @@
         <v>30</v>
       </c>
       <c r="O56" s="6" t="n">
-        <v>550</v>
+        <v>142</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>142</v>
+        <v>7.9</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>7.9</v>
+        <v>35879</v>
       </c>
       <c r="R56" s="6" t="n">
-        <v>35879</v>
+        <v>1</v>
       </c>
       <c r="S56" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" s="6" t="inlineStr">
+      <c r="U56" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V56" s="6" t="n">
+        <v>28.53545531224325</v>
+      </c>
       <c r="W56" s="6" t="n">
-        <v>28.53545531224325</v>
+        <v>-82.1186953043933</v>
       </c>
       <c r="X56" s="6" t="n">
-        <v>-82.1186953043933</v>
-      </c>
-      <c r="Y56" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Z56" s="6" t="inlineStr">
+      <c r="Y56" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 11 spp. observed (4 bird / 7 amphibian); 30 EPA PFAS facilities of 550 FRS records; adult asthma 7.9%; contaminant samples in county: 0</t>
         </is>
@@ -5766,16 +5595,16 @@
         <v>8</v>
       </c>
       <c r="O57" s="6" t="n">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>141</v>
+        <v>9.9</v>
       </c>
       <c r="Q57" s="6" t="n">
-        <v>9.9</v>
+        <v>15532</v>
       </c>
       <c r="R57" s="6" t="n">
-        <v>15532</v>
+        <v>0</v>
       </c>
       <c r="S57" s="6" t="n">
         <v>0</v>
@@ -5783,24 +5612,21 @@
       <c r="T57" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" s="6" t="inlineStr">
+      <c r="U57" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V57" s="6" t="n">
+        <v>30.5237846237284</v>
+      </c>
       <c r="W57" s="6" t="n">
-        <v>30.5237846237284</v>
+        <v>-82.96235429911742</v>
       </c>
       <c r="X57" s="6" t="n">
-        <v>-82.96235429911742</v>
-      </c>
-      <c r="Y57" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z57" s="6" t="inlineStr">
+      <c r="Y57" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 4 spp. observed (1 bird / 3 amphibian); 8 EPA PFAS facilities of 122 FRS records; adult asthma 9.9%; contaminant samples in county: 0</t>
         </is>
@@ -5858,16 +5684,16 @@
         <v>17</v>
       </c>
       <c r="O58" s="6" t="n">
-        <v>263</v>
+        <v>141</v>
       </c>
       <c r="P58" s="6" t="n">
-        <v>141</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q58" s="6" t="n">
-        <v>8.800000000000001</v>
+        <v>18193</v>
       </c>
       <c r="R58" s="6" t="n">
-        <v>18193</v>
+        <v>0</v>
       </c>
       <c r="S58" s="6" t="n">
         <v>0</v>
@@ -5875,24 +5701,21 @@
       <c r="T58" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="6" t="inlineStr">
+      <c r="U58" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V58" s="6" t="n">
+        <v>27.15938340081132</v>
+      </c>
       <c r="W58" s="6" t="n">
-        <v>27.15938340081132</v>
+        <v>-81.74374798691413</v>
       </c>
       <c r="X58" s="6" t="n">
-        <v>-81.74374798691413</v>
-      </c>
-      <c r="Y58" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z58" s="6" t="inlineStr">
+      <c r="Y58" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 6 spp. observed (4 bird / 2 amphibian); 17 EPA PFAS facilities of 263 FRS records; adult asthma 8.8%; contaminant samples in county: 0</t>
         </is>
@@ -5950,16 +5773,16 @@
         <v>11</v>
       </c>
       <c r="O59" s="6" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="P59" s="6" t="n">
-        <v>140</v>
+        <v>9.5</v>
       </c>
       <c r="Q59" s="6" t="n">
-        <v>9.5</v>
+        <v>22775</v>
       </c>
       <c r="R59" s="6" t="n">
-        <v>22775</v>
+        <v>0</v>
       </c>
       <c r="S59" s="6" t="n">
         <v>0</v>
@@ -5967,24 +5790,21 @@
       <c r="T59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="6" t="inlineStr">
+      <c r="U59" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V59" s="6" t="n">
+        <v>29.70267721799804</v>
+      </c>
       <c r="W59" s="6" t="n">
-        <v>29.70267721799804</v>
+        <v>-82.79035312255256</v>
       </c>
       <c r="X59" s="6" t="n">
-        <v>-82.79035312255256</v>
-      </c>
-      <c r="Y59" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z59" s="6" t="inlineStr">
+      <c r="Y59" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 1 spp. observed (0 bird / 1 amphibian); 11 EPA PFAS facilities of 123 FRS records; adult asthma 9.5%; contaminant samples in county: 0</t>
         </is>
@@ -6042,16 +5862,16 @@
         <v>13</v>
       </c>
       <c r="O60" s="6" t="n">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="P60" s="6" t="n">
-        <v>140</v>
+        <v>9.1</v>
       </c>
       <c r="Q60" s="6" t="n">
-        <v>9.1</v>
+        <v>19512</v>
       </c>
       <c r="R60" s="6" t="n">
-        <v>19512</v>
+        <v>0</v>
       </c>
       <c r="S60" s="6" t="n">
         <v>0</v>
@@ -6059,24 +5879,21 @@
       <c r="T60" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="6" t="inlineStr">
+      <c r="U60" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V60" s="6" t="n">
+        <v>30.3946890531829</v>
+      </c>
       <c r="W60" s="6" t="n">
-        <v>30.3946890531829</v>
+        <v>-85.27724460622655</v>
       </c>
       <c r="X60" s="6" t="n">
-        <v>-85.27724460622655</v>
-      </c>
-      <c r="Y60" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z60" s="6" t="inlineStr">
+      <c r="Y60" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 3 spp. observed (0 bird / 3 amphibian); 13 EPA PFAS facilities of 117 FRS records; adult asthma 9.1%; contaminant samples in county: 0</t>
         </is>
@@ -6134,16 +5951,16 @@
         <v>6</v>
       </c>
       <c r="O61" s="6" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="P61" s="6" t="n">
-        <v>140</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q61" s="6" t="n">
-        <v>9.300000000000001</v>
+        <v>24051</v>
       </c>
       <c r="R61" s="6" t="n">
-        <v>24051</v>
+        <v>0</v>
       </c>
       <c r="S61" s="6" t="n">
         <v>0</v>
@@ -6151,24 +5968,21 @@
       <c r="T61" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="6" t="inlineStr">
+      <c r="U61" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V61" s="6" t="n">
+        <v>30.45721609635384</v>
+      </c>
       <c r="W61" s="6" t="n">
-        <v>30.45721609635384</v>
+        <v>-82.25650767548719</v>
       </c>
       <c r="X61" s="6" t="n">
-        <v>-82.25650767548719</v>
-      </c>
-      <c r="Y61" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z61" s="6" t="inlineStr">
+      <c r="Y61" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 13 spp. observed (0 bird / 13 amphibian); 6 EPA PFAS facilities of 150 FRS records; adult asthma 9.3%; contaminant samples in county: 0</t>
         </is>
@@ -6226,16 +6040,16 @@
         <v>10</v>
       </c>
       <c r="O62" s="6" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="P62" s="6" t="n">
-        <v>140</v>
+        <v>9</v>
       </c>
       <c r="Q62" s="6" t="n">
-        <v>9</v>
+        <v>22128</v>
       </c>
       <c r="R62" s="6" t="n">
-        <v>22128</v>
+        <v>0</v>
       </c>
       <c r="S62" s="6" t="n">
         <v>0</v>
@@ -6243,24 +6057,21 @@
       <c r="T62" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="6" t="inlineStr">
+      <c r="U62" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V62" s="6" t="n">
+        <v>26.99720319571579</v>
+      </c>
       <c r="W62" s="6" t="n">
-        <v>26.99720319571579</v>
+        <v>-81.37816793850926</v>
       </c>
       <c r="X62" s="6" t="n">
-        <v>-81.37816793850926</v>
-      </c>
-      <c r="Y62" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z62" s="6" t="inlineStr">
+      <c r="Y62" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 6 spp. observed (1 bird / 5 amphibian); 10 EPA PFAS facilities of 200 FRS records; adult asthma 9.0%; contaminant samples in county: 0</t>
         </is>
@@ -6318,41 +6129,38 @@
         <v>12</v>
       </c>
       <c r="O63" s="6" t="n">
-        <v>605</v>
+        <v>142</v>
       </c>
       <c r="P63" s="6" t="n">
-        <v>142</v>
+        <v>8.5</v>
       </c>
       <c r="Q63" s="6" t="n">
-        <v>8.5</v>
+        <v>32722</v>
       </c>
       <c r="R63" s="6" t="n">
-        <v>32722</v>
+        <v>1</v>
       </c>
       <c r="S63" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" s="6" t="inlineStr">
+      <c r="U63" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V63" s="6" t="n">
+        <v>29.44175296054901</v>
+      </c>
       <c r="W63" s="6" t="n">
-        <v>29.44175296054901</v>
+        <v>-81.37840920315203</v>
       </c>
       <c r="X63" s="6" t="n">
-        <v>-81.37840920315203</v>
-      </c>
-      <c r="Y63" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Z63" s="6" t="inlineStr">
+      <c r="Y63" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 8 spp. observed (2 bird / 6 amphibian); 12 EPA PFAS facilities of 605 FRS records; adult asthma 8.5%; contaminant samples in county: 0</t>
         </is>
@@ -6410,16 +6218,16 @@
         <v>9</v>
       </c>
       <c r="O64" s="6" t="n">
-        <v>203</v>
+        <v>140</v>
       </c>
       <c r="P64" s="6" t="n">
-        <v>140</v>
+        <v>8.9</v>
       </c>
       <c r="Q64" s="6" t="n">
-        <v>8.9</v>
+        <v>20181</v>
       </c>
       <c r="R64" s="6" t="n">
-        <v>20181</v>
+        <v>0</v>
       </c>
       <c r="S64" s="6" t="n">
         <v>0</v>
@@ -6427,24 +6235,21 @@
       <c r="T64" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="6" t="inlineStr">
+      <c r="U64" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V64" s="6" t="n">
+        <v>27.44650041645728</v>
+      </c>
       <c r="W64" s="6" t="n">
-        <v>27.44650041645728</v>
+        <v>-81.72937125003942</v>
       </c>
       <c r="X64" s="6" t="n">
-        <v>-81.72937125003942</v>
-      </c>
-      <c r="Y64" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z64" s="6" t="inlineStr">
+      <c r="Y64" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 5 spp. observed (2 bird / 3 amphibian); 9 EPA PFAS facilities of 203 FRS records; adult asthma 8.9%; contaminant samples in county: 0</t>
         </is>
@@ -6502,16 +6307,16 @@
         <v>5</v>
       </c>
       <c r="O65" s="6" t="n">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="P65" s="6" t="n">
-        <v>140</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q65" s="6" t="n">
-        <v>9.199999999999999</v>
+        <v>17022</v>
       </c>
       <c r="R65" s="6" t="n">
-        <v>17022</v>
+        <v>0</v>
       </c>
       <c r="S65" s="6" t="n">
         <v>0</v>
@@ -6519,31 +6324,28 @@
       <c r="T65" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="6" t="inlineStr">
+      <c r="U65" s="6" t="inlineStr">
         <is>
           <t>verified L8</t>
         </is>
       </c>
+      <c r="V65" s="6" t="n">
+        <v>29.98566043741613</v>
+      </c>
       <c r="W65" s="6" t="n">
-        <v>29.98566043741613</v>
+        <v>-83.05917885028005</v>
       </c>
       <c r="X65" s="6" t="n">
-        <v>-83.05917885028005</v>
-      </c>
-      <c r="Y65" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Z65" s="6" t="inlineStr">
+      <c r="Y65" s="7" t="inlineStr">
         <is>
           <t>0 sentinel-capable sp. (best tier none); 0 pathogen-host sp.; 4 spp. observed (1 bird / 3 amphibian); 5 EPA PFAS facilities of 83 FRS records; adult asthma 9.2%; contaminant samples in county: 0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z65"/>
+  <autoFilter ref="A1:Y65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11959,7 +11761,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>fiokg EPA-PFAS-Facility records per county (4,118 in Florida; 188,057 nationally) — the PFAS-relevant subset of the EPA Facility Registry Service. All-FRS counts (118,663 in Florida of 4,955,792 nationally) are reported as a column but do NOT enter the score: FRS registers every site ever regulated or reported by EPA or a state programme, so it indexes economic activity more than PFAS risk. Verified 2026-07-29: log10 of the two measures correlates r = 0.943 across the 64 study counties, the top 8 counties are identical under either proxy, and the median absolute rank shift is 1 (max 12).</t>
+          <t>fiokg EPA-PFAS-Facility records per county (4,118 in Florida; 188,057 nationally) — the PFAS-relevant subset of the EPA Facility Registry Service. All-programme FRS counts are NOT used anywhere in this study: FRS registers every site ever regulated or reported by EPA or a state programme, so it indexes economic activity more than PFAS risk. Verified 2026-07-29: log10 of the two measures correlates r = 0.943 across the 64 study counties, the top 8 counties are identical under either proxy, and the median absolute rank shift is 1 (max 12).</t>
         </is>
       </c>
     </row>
